--- a/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2669.4</v>
+        <v>38373.75</v>
       </c>
       <c r="C4" t="n">
-        <v>502992</v>
+        <v>4358592</v>
       </c>
       <c r="D4" t="n">
-        <v>395208</v>
+        <v>3424608</v>
       </c>
       <c r="E4" t="n">
-        <v>90000</v>
+        <v>811800</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>6930</v>
+        <v>89850</v>
       </c>
       <c r="H4" t="n">
-        <v>180</v>
+        <v>15240</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20640</v>
+        <v>215400</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3293.73</v>
+        <v>17399.88</v>
       </c>
       <c r="C5" t="n">
-        <v>482328</v>
+        <v>1317960</v>
       </c>
       <c r="D5" t="n">
-        <v>378972</v>
+        <v>1035540</v>
       </c>
       <c r="E5" t="n">
-        <v>81900</v>
+        <v>136800</v>
       </c>
       <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28830</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3570</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>6630</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>21750</v>
+        <v>91620</v>
       </c>
     </row>
     <row r="6">
@@ -9919,25 +9913,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3197.79</v>
+        <v>2847.42</v>
       </c>
       <c r="C6" t="n">
-        <v>269640</v>
+        <v>227808</v>
       </c>
       <c r="D6" t="n">
-        <v>211860</v>
+        <v>178992</v>
       </c>
       <c r="E6" t="n">
-        <v>30600</v>
+        <v>2700</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5970</v>
+        <v>6480</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9949,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10470</v>
+        <v>29070</v>
       </c>
     </row>
     <row r="7">
@@ -9957,22 +9951,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2242.35</v>
+        <v>1299.78</v>
       </c>
       <c r="C7" t="n">
-        <v>140112</v>
+        <v>48384</v>
       </c>
       <c r="D7" t="n">
-        <v>110088</v>
+        <v>38016</v>
       </c>
       <c r="E7" t="n">
-        <v>7200</v>
+        <v>900</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4050</v>
+        <v>780</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9987,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6000</v>
+        <v>11430</v>
       </c>
     </row>
     <row r="8">
@@ -9995,22 +9989,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1250.1</v>
+        <v>140.13</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>3024</v>
       </c>
       <c r="D8" t="n">
-        <v>41184</v>
+        <v>2376</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1410</v>
+        <v>540</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10025,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3510</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="9">
@@ -10033,25 +10027,25 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>614.0700000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>1512</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>1188</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>240</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>540</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="10">
@@ -10071,13 +10065,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>381.06</v>
+        <v>50.04</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>3024</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>2376</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10086,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>450</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.19</v>
+        <v>12.78</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>5040</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>3960</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>3600</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12">
@@ -10147,13 +10141,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>6.03</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>396</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10162,7 +10156,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.66</v>
+        <v>3.06</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -10223,13 +10217,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>0.72</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10238,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10299,7 +10293,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -10337,7 +10331,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1482.18</v>
+        <v>7829.95</v>
       </c>
       <c r="C5" t="n">
-        <v>265280.4</v>
+        <v>724878</v>
       </c>
       <c r="D5" t="n">
-        <v>125439.73</v>
+        <v>342763.74</v>
       </c>
       <c r="E5" t="n">
-        <v>9033.57</v>
+        <v>15089.04</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1285.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4567.5</v>
+        <v>19240.2</v>
       </c>
     </row>
     <row r="6">
@@ -11783,25 +11777,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2558.23</v>
+        <v>2277.94</v>
       </c>
       <c r="C6" t="n">
-        <v>242676</v>
+        <v>205027.2</v>
       </c>
       <c r="D6" t="n">
-        <v>107413.02</v>
+        <v>90748.94</v>
       </c>
       <c r="E6" t="n">
-        <v>5171.4</v>
+        <v>456.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>298.5</v>
+        <v>324</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>273.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11813,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3873.9</v>
+        <v>10755.9</v>
       </c>
     </row>
     <row r="7">
@@ -11821,22 +11815,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2130.23</v>
+        <v>1234.79</v>
       </c>
       <c r="C7" t="n">
-        <v>140112</v>
+        <v>48384</v>
       </c>
       <c r="D7" t="n">
-        <v>70236.14</v>
+        <v>24254.21</v>
       </c>
       <c r="E7" t="n">
-        <v>1531.44</v>
+        <v>191.43</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>607.5</v>
+        <v>117</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -11851,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3600</v>
+        <v>6858</v>
       </c>
     </row>
     <row r="8">
@@ -11859,22 +11853,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1250.1</v>
+        <v>140.13</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>3024</v>
       </c>
       <c r="D8" t="n">
-        <v>30311.42</v>
+        <v>1748.74</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>916.5</v>
+        <v>351</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -11889,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2492.1</v>
+        <v>3067.2</v>
       </c>
     </row>
     <row r="9">
@@ -11897,25 +11891,25 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>614.0700000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>1512</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>953.96</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>204</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>437.4</v>
+        <v>2527.2</v>
       </c>
     </row>
     <row r="10">
@@ -11935,13 +11929,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>381.06</v>
+        <v>50.04</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>3024</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>2067.12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11950,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>400.5</v>
+        <v>1949.1</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.19</v>
+        <v>12.78</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>5040</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>3558.06</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>3600</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12">
@@ -12011,13 +12005,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>6.03</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>367.09</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12026,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.66</v>
+        <v>3.06</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1128.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -12087,13 +12081,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>0.72</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12102,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>780.91</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12163,7 +12157,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -12201,7 +12195,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3260792.7</v>
+        <v>17225881.2</v>
       </c>
       <c r="C5" t="n">
-        <v>14590422</v>
+        <v>39868290</v>
       </c>
       <c r="D5" t="n">
-        <v>12710808.04</v>
+        <v>34732249.77</v>
       </c>
       <c r="E5" t="n">
-        <v>1664344.94</v>
+        <v>2780004.73</v>
       </c>
       <c r="F5" t="n">
-        <v>3333.36</v>
+        <v>4166.7</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>355550.58</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>69999.60000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>43025.85</v>
+        <v>181242.68</v>
       </c>
     </row>
     <row r="6">
@@ -12715,25 +12709,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>5628110.4</v>
+        <v>5011459.2</v>
       </c>
       <c r="C6" t="n">
-        <v>13347180</v>
+        <v>11276496</v>
       </c>
       <c r="D6" t="n">
-        <v>10884161.32</v>
+        <v>9195590.5</v>
       </c>
       <c r="E6" t="n">
-        <v>952778.74</v>
+        <v>84068.71000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>12500.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5522.25</v>
+        <v>5994</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>75691.44</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12745,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>36492.14</v>
+        <v>101320.58</v>
       </c>
     </row>
     <row r="7">
@@ -12753,22 +12747,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4686511.5</v>
+        <v>2716540.2</v>
       </c>
       <c r="C7" t="n">
-        <v>7706160</v>
+        <v>2661120</v>
       </c>
       <c r="D7" t="n">
-        <v>7117028.47</v>
+        <v>2457678.9</v>
       </c>
       <c r="E7" t="n">
-        <v>282152.51</v>
+        <v>35269.06</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>11238.75</v>
+        <v>2164.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -12783,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>33912</v>
+        <v>64602.36</v>
       </c>
     </row>
     <row r="8">
@@ -12791,22 +12785,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2750220</v>
+        <v>308286</v>
       </c>
       <c r="C8" t="n">
-        <v>2882880</v>
+        <v>166320</v>
       </c>
       <c r="D8" t="n">
-        <v>3071456.59</v>
+        <v>177199.42</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16955.25</v>
+        <v>6493.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12821,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23475.58</v>
+        <v>28893.02</v>
       </c>
     </row>
     <row r="9">
@@ -12829,25 +12823,25 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1350954</v>
+        <v>219780</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>83160</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>96665.17</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>3774</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4120.31</v>
+        <v>23806.22</v>
       </c>
     </row>
     <row r="10">
@@ -12867,13 +12861,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>838332</v>
+        <v>110088</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>166320</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>209461.27</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12882,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>4995</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3772.71</v>
+        <v>18360.52</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>473418</v>
+        <v>28116</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>277200</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>360538.22</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>66600</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="12">
@@ -12943,13 +12937,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345312</v>
+        <v>13266</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>27720</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>37197.43</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12958,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>555</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>371052</v>
+        <v>6732</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>114300.85</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13019,13 +13013,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94248</v>
+        <v>1584</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13034,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>79129.81</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13095,7 +13089,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -13133,7 +13127,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>38373.75</v>
+        <v>9489.690000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>4358592</v>
+        <v>1020600</v>
       </c>
       <c r="D4" t="n">
-        <v>3424608</v>
+        <v>801900</v>
       </c>
       <c r="E4" t="n">
-        <v>811800</v>
+        <v>426600</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>89850</v>
+        <v>28920</v>
       </c>
       <c r="H4" t="n">
-        <v>15240</v>
+        <v>2670</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>215400</v>
+        <v>111750</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>17399.88</v>
+        <v>1206.09</v>
       </c>
       <c r="C5" t="n">
-        <v>1317960</v>
+        <v>141624</v>
       </c>
       <c r="D5" t="n">
-        <v>1035540</v>
+        <v>111276</v>
       </c>
       <c r="E5" t="n">
-        <v>136800</v>
+        <v>42300</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>28830</v>
+        <v>3840</v>
       </c>
       <c r="H5" t="n">
-        <v>3570</v>
+        <v>360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>91620</v>
+        <v>24480</v>
       </c>
     </row>
     <row r="6">
@@ -13647,13 +13641,13 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2847.42</v>
+        <v>133.65</v>
       </c>
       <c r="C6" t="n">
-        <v>227808</v>
+        <v>11592</v>
       </c>
       <c r="D6" t="n">
-        <v>178992</v>
+        <v>9108</v>
       </c>
       <c r="E6" t="n">
         <v>2700</v>
@@ -13662,10 +13656,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6480</v>
+        <v>240</v>
       </c>
       <c r="H6" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -13677,7 +13671,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>29070</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="7">
@@ -13685,22 +13679,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>1299.78</v>
+        <v>40.68</v>
       </c>
       <c r="C7" t="n">
-        <v>48384</v>
+        <v>504</v>
       </c>
       <c r="D7" t="n">
-        <v>38016</v>
+        <v>396</v>
       </c>
       <c r="E7" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>780</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -13715,7 +13709,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>11430</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -13723,13 +13717,13 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>140.13</v>
+        <v>0.36</v>
       </c>
       <c r="C8" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13738,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>540</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -13753,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4320</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -13761,13 +13755,13 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13776,10 +13770,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -13799,13 +13793,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>50.04</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13814,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2190</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -13837,13 +13831,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>12.78</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5040</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13852,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -13875,13 +13869,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13890,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13951,7 +13945,7 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13992,10 +13986,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14106,10 +14100,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14144,10 +14138,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>7829.95</v>
+        <v>542.74</v>
       </c>
       <c r="C5" t="n">
-        <v>724878</v>
+        <v>77893.2</v>
       </c>
       <c r="D5" t="n">
-        <v>342763.74</v>
+        <v>36832.36</v>
       </c>
       <c r="E5" t="n">
-        <v>15089.04</v>
+        <v>4665.69</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1285.2</v>
+        <v>129.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>19240.2</v>
+        <v>5140.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,13 +14573,13 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2277.94</v>
+        <v>106.92</v>
       </c>
       <c r="C6" t="n">
-        <v>205027.2</v>
+        <v>10432.8</v>
       </c>
       <c r="D6" t="n">
-        <v>90748.94</v>
+        <v>4617.76</v>
       </c>
       <c r="E6" t="n">
         <v>456.3</v>
@@ -14594,10 +14588,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>324</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>273.6</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -14609,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10755.9</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="7">
@@ -14617,22 +14611,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>1234.79</v>
+        <v>38.65</v>
       </c>
       <c r="C7" t="n">
-        <v>48384</v>
+        <v>504</v>
       </c>
       <c r="D7" t="n">
-        <v>24254.21</v>
+        <v>252.65</v>
       </c>
       <c r="E7" t="n">
-        <v>191.43</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>117</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -14647,7 +14641,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6858</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -14655,13 +14649,13 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>140.13</v>
+        <v>0.36</v>
       </c>
       <c r="C8" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1748.74</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14670,7 +14664,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>351</v>
+        <v>19.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14685,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3067.2</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="9">
@@ -14693,13 +14687,13 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>953.96</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14708,10 +14702,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>204</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2527.2</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="10">
@@ -14731,13 +14725,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>50.04</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2067.12</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14746,7 +14740,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1949.1</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -14769,13 +14763,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>12.78</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5040</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3558.06</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14784,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14807,13 +14801,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>367.09</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14822,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1128.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14883,7 +14877,7 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14924,10 +14918,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>780.91</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15038,10 +15032,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15076,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>17225881.2</v>
+        <v>1194029.1</v>
       </c>
       <c r="C5" t="n">
-        <v>39868290</v>
+        <v>4284126</v>
       </c>
       <c r="D5" t="n">
-        <v>34732249.77</v>
+        <v>3732222.63</v>
       </c>
       <c r="E5" t="n">
-        <v>2780004.73</v>
+        <v>859606.73</v>
       </c>
       <c r="F5" t="n">
-        <v>4166.7</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>355550.58</v>
+        <v>35853.84</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>69999.60000000001</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>181242.68</v>
+        <v>48426.34</v>
       </c>
     </row>
     <row r="6">
@@ -15511,13 +15505,13 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>5011459.2</v>
+        <v>235224</v>
       </c>
       <c r="C6" t="n">
-        <v>11276496</v>
+        <v>573804</v>
       </c>
       <c r="D6" t="n">
-        <v>9195590.5</v>
+        <v>467917.22</v>
       </c>
       <c r="E6" t="n">
         <v>84068.71000000001</v>
@@ -15526,10 +15520,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5994</v>
+        <v>222</v>
       </c>
       <c r="H6" t="n">
-        <v>75691.44</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15541,7 +15535,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>101320.58</v>
+        <v>15684.3</v>
       </c>
     </row>
     <row r="7">
@@ -15549,22 +15543,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2716540.2</v>
+        <v>85021.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2661120</v>
+        <v>27720</v>
       </c>
       <c r="D7" t="n">
-        <v>2457678.9</v>
+        <v>25600.82</v>
       </c>
       <c r="E7" t="n">
-        <v>35269.06</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2164.5</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15579,7 +15573,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>64602.36</v>
+        <v>1017.36</v>
       </c>
     </row>
     <row r="8">
@@ -15587,13 +15581,13 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>308286</v>
+        <v>792</v>
       </c>
       <c r="C8" t="n">
-        <v>166320</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>177199.42</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15602,7 +15596,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6493.5</v>
+        <v>360.75</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15617,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>28893.02</v>
+        <v>401.29</v>
       </c>
     </row>
     <row r="9">
@@ -15625,13 +15619,13 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>219780</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15640,10 +15634,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3774</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15655,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>23806.22</v>
+        <v>1373.44</v>
       </c>
     </row>
     <row r="10">
@@ -15663,13 +15657,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>110088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>166320</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>209461.27</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15678,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4995</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15693,4667 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>18360.52</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>28116</v>
-      </c>
-      <c r="C11" t="n">
-        <v>277200</v>
-      </c>
-      <c r="D11" t="n">
-        <v>360538.22</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>66600</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>13266</v>
-      </c>
-      <c r="C12" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D12" t="n">
-        <v>37197.43</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>555</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>6732</v>
-      </c>
-      <c r="C13" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D13" t="n">
-        <v>114300.85</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1584</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D15" t="n">
-        <v>79129.81</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D19" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D22" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3447.99</v>
-      </c>
-      <c r="C4" t="n">
-        <v>431424</v>
-      </c>
-      <c r="D4" t="n">
-        <v>338976</v>
-      </c>
-      <c r="E4" t="n">
-        <v>134100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4890</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2160</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15840</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4406.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>353808</v>
-      </c>
-      <c r="D5" t="n">
-        <v>277992</v>
-      </c>
-      <c r="E5" t="n">
-        <v>63000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5400</v>
-      </c>
-      <c r="H5" t="n">
-        <v>630</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9540</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4280.31</v>
-      </c>
-      <c r="C6" t="n">
-        <v>241920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>190080</v>
-      </c>
-      <c r="E6" t="n">
-        <v>45900</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3960</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8400</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3411.72</v>
-      </c>
-      <c r="C7" t="n">
-        <v>161280</v>
-      </c>
-      <c r="D7" t="n">
-        <v>126720</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17100</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3150</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>10770</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2473.38</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D8" t="n">
-        <v>43560</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2070</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1687.59</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D9" t="n">
-        <v>21780</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>330</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>882.09</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4356</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>526.59</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>396.99</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>367.29</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>242.37</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1982.88</v>
-      </c>
-      <c r="C5" t="n">
-        <v>194594.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>92015.35000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6948.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>226.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2003.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3424.25</v>
-      </c>
-      <c r="C6" t="n">
-        <v>217728</v>
-      </c>
-      <c r="D6" t="n">
-        <v>96370.56</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7757.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>198</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3108</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3241.13</v>
-      </c>
-      <c r="C7" t="n">
-        <v>161280</v>
-      </c>
-      <c r="D7" t="n">
-        <v>80847.36</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3637.17</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6462</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2473.38</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D8" t="n">
-        <v>32060.16</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1345.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3195</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1687.59</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D9" t="n">
-        <v>17489.34</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>280.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>882.09</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3789.72</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>526.59</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>396.99</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>367.29</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>242.37</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4362336</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10702692</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9323915.619999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1280265.34</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2500.02</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>62744.22</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>18872.03</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7533345.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>11975040</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9765228.84</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1429168.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3663</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>29277.36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7130494.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8870400</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8192262.99</v>
-      </c>
-      <c r="E7" t="n">
-        <v>670112.2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8741.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>60872.04</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5441436</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3049200</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3248656.01</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24891.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>30096.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3712698</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1524600</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1772194.82</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5189.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6867.18</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1940598</v>
-      </c>
-      <c r="C10" t="n">
-        <v>304920</v>
-      </c>
-      <c r="D10" t="n">
-        <v>384012.33</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1158498</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>873378</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>808038</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1081278</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>533214</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>94050</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>59400</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>9489.690000000001</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1020600</v>
-      </c>
-      <c r="D4" t="n">
-        <v>801900</v>
-      </c>
-      <c r="E4" t="n">
-        <v>426600</v>
-      </c>
-      <c r="F4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G4" t="n">
-        <v>28920</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2670</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>111750</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1206.09</v>
-      </c>
-      <c r="C5" t="n">
-        <v>141624</v>
-      </c>
-      <c r="D5" t="n">
-        <v>111276</v>
-      </c>
-      <c r="E5" t="n">
-        <v>42300</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3840</v>
-      </c>
-      <c r="H5" t="n">
-        <v>360</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>24480</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>133.65</v>
-      </c>
-      <c r="C6" t="n">
-        <v>11592</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9108</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>240</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="C7" t="n">
-        <v>504</v>
-      </c>
-      <c r="D7" t="n">
-        <v>396</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>542.74</v>
-      </c>
-      <c r="C5" t="n">
-        <v>77893.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>36832.36</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4665.69</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>129.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5140.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>106.92</v>
-      </c>
-      <c r="C6" t="n">
-        <v>10432.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4617.76</v>
-      </c>
-      <c r="E6" t="n">
-        <v>456.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1665</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="C7" t="n">
-        <v>504</v>
-      </c>
-      <c r="D7" t="n">
-        <v>252.65</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>42.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>145.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>80.09999999999999</v>
+        <v>754.54</v>
       </c>
     </row>
     <row r="11">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1194029.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4284126</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3732222.63</v>
-      </c>
-      <c r="E5" t="n">
-        <v>859606.73</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>35853.84</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>48426.34</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>235224</v>
-      </c>
-      <c r="C6" t="n">
-        <v>573804</v>
-      </c>
-      <c r="D6" t="n">
-        <v>467917.22</v>
-      </c>
-      <c r="E6" t="n">
-        <v>84068.71000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>222</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15684.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>85021.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D7" t="n">
-        <v>25600.82</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1017.36</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>792</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>360.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>401.29</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1373.44</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>754.54</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>59580</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>28</v>
@@ -576,7 +576,7 @@
         <v>12270</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -1508,7 +1508,7 @@
         <v>2130</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>766.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>212135.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>15240</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
@@ -9896,7 +9896,7 @@
         <v>3570</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -10828,7 +10828,7 @@
         <v>4417.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
@@ -11760,7 +11760,7 @@
         <v>1285.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>1.2</v>
@@ -12692,7 +12692,7 @@
         <v>355550.58</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>69999.60000000001</v>
@@ -16420,7 +16420,7 @@
         <v>1222018.38</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>139999.2</v>
@@ -17314,7 +17314,7 @@
         <v>3750</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>

--- a/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="L4" t="n">
         <v>923790</v>
@@ -582,7 +582,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="L5" t="n">
         <v>339750</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L6" t="n">
         <v>106950</v>
@@ -658,7 +658,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
         <v>50550</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>19020</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>7410</v>
@@ -1476,7 +1476,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L4" t="n">
         <v>72900</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
         <v>44250</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>22890</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>9720</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>960</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>11.76</v>
       </c>
       <c r="L5" t="n">
         <v>9292.5</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="L6" t="n">
         <v>8469.299999999999</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>5832</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>777.6</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>250887.84</v>
       </c>
       <c r="L5" t="n">
         <v>87535.35000000001</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>208006.5</v>
       </c>
       <c r="L6" t="n">
         <v>79780.81</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>54937.44</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L9" t="n">
         <v>7324.99</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
         <v>46800</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>7680</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>1230</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="L5" t="n">
         <v>1612.8</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>455.1</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>26880.84</v>
       </c>
       <c r="L5" t="n">
         <v>15192.58</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>4287.04</v>
@@ -7068,7 +7068,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
         <v>14610</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>4320</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>300</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="L5" t="n">
         <v>907.2</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>111</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>44801.4</v>
       </c>
       <c r="L5" t="n">
         <v>8545.82</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>1045.62</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>169.56</v>
@@ -9864,7 +9864,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="L4" t="n">
         <v>215400</v>
@@ -9902,7 +9902,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>91620</v>
@@ -9940,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
         <v>29070</v>
@@ -9978,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>11430</v>
@@ -10834,7 +10834,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>86.94</v>
       </c>
       <c r="L5" t="n">
         <v>71347.5</v>
@@ -10872,7 +10872,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>30.55</v>
       </c>
       <c r="L6" t="n">
         <v>39571.5</v>
@@ -10910,7 +10910,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>9.84</v>
       </c>
       <c r="L7" t="n">
         <v>30330</v>
@@ -10948,7 +10948,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>13504.2</v>
@@ -10986,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>6002.1</v>
@@ -11766,7 +11766,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="L5" t="n">
         <v>19240.2</v>
@@ -11804,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="L6" t="n">
         <v>10755.9</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="n">
         <v>6858</v>
@@ -12698,7 +12698,7 @@
         <v>69999.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>537616.8</v>
       </c>
       <c r="L5" t="n">
         <v>181242.68</v>
@@ -12736,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>166405.2</v>
       </c>
       <c r="L6" t="n">
         <v>101320.58</v>
@@ -12774,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>69975.52</v>
       </c>
       <c r="L7" t="n">
         <v>64602.36</v>
@@ -13592,7 +13592,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
         <v>111750</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>24480</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="L5" t="n">
         <v>5140.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>17920.56</v>
       </c>
       <c r="L5" t="n">
         <v>48426.34</v>
@@ -16426,7 +16426,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1854777.96</v>
       </c>
       <c r="L5" t="n">
         <v>672093.45</v>
@@ -16464,7 +16464,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>651753.7</v>
       </c>
       <c r="L6" t="n">
         <v>372763.53</v>
@@ -16502,7 +16502,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>209926.56</v>
       </c>
       <c r="L7" t="n">
         <v>285708.6</v>
@@ -16540,7 +16540,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>76802.39999999999</v>
       </c>
       <c r="L8" t="n">
         <v>127209.56</v>
@@ -16578,7 +16578,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>128004</v>
       </c>
       <c r="L9" t="n">
         <v>56539.78</v>
@@ -17320,7 +17320,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="L4" t="n">
         <v>178110</v>
@@ -17358,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L5" t="n">
         <v>69120</v>
@@ -17396,7 +17396,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
         <v>21720</v>
@@ -17434,7 +17434,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>8820</v>
@@ -17472,7 +17472,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>2670</v>
@@ -17510,7 +17510,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>1110</v>
@@ -18290,7 +18290,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>26.46</v>
       </c>
       <c r="L5" t="n">
         <v>14515.2</v>
@@ -18328,7 +18328,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>8036.4</v>
@@ -18366,7 +18366,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="n">
         <v>5292</v>
@@ -18404,7 +18404,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
         <v>1895.7</v>
@@ -18442,7 +18442,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>899.1</v>
@@ -19222,7 +19222,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>564497.64</v>
       </c>
       <c r="L5" t="n">
         <v>136733.18</v>
@@ -19260,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>180272.3</v>
       </c>
       <c r="L6" t="n">
         <v>75702.89</v>
@@ -19298,7 +19298,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>69975.52</v>
       </c>
       <c r="L7" t="n">
         <v>49850.64</v>
@@ -19336,7 +19336,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57601.8</v>
       </c>
       <c r="L8" t="n">
         <v>17857.49</v>
@@ -19374,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>8469.52</v>
@@ -20116,7 +20116,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="L4" t="n">
         <v>240780</v>
@@ -20154,7 +20154,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
         <v>62820</v>
@@ -20192,7 +20192,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>7440</v>
@@ -21086,7 +21086,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>18.48</v>
       </c>
       <c r="L5" t="n">
         <v>13192.2</v>
@@ -21124,7 +21124,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="L6" t="n">
         <v>2752.8</v>
@@ -22018,7 +22018,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>394252.32</v>
       </c>
       <c r="L5" t="n">
         <v>124270.52</v>
@@ -22056,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>55468.4</v>
       </c>
       <c r="L6" t="n">
         <v>25931.38</v>

--- a/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>120722.31</v>
+        <v>120638.07</v>
       </c>
       <c r="C4" t="n">
         <v>18326952</v>
@@ -532,7 +537,7 @@
         <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>357570</v>
+        <v>355710</v>
       </c>
       <c r="H4" t="n">
         <v>59580</v>
@@ -544,10 +549,13 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="L4" t="n">
-        <v>923790</v>
+        <v>920130</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42570</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>52615.98</v>
+        <v>52590.33</v>
       </c>
       <c r="C5" t="n">
         <v>5585832</v>
@@ -570,7 +578,7 @@
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>133560</v>
+        <v>133020</v>
       </c>
       <c r="H5" t="n">
         <v>12270</v>
@@ -582,10 +590,13 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L5" t="n">
-        <v>339750</v>
+        <v>338790</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20340</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>21634.74</v>
+        <v>21633.66</v>
       </c>
       <c r="C6" t="n">
         <v>1606248</v>
@@ -608,7 +619,7 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>44520</v>
+        <v>44160</v>
       </c>
       <c r="H6" t="n">
         <v>4320</v>
@@ -620,10 +631,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L6" t="n">
-        <v>106950</v>
+        <v>106320</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7770</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>13110.48</v>
+        <v>13110.39</v>
       </c>
       <c r="C7" t="n">
         <v>598248</v>
@@ -646,7 +660,7 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>17520</v>
+        <v>17220</v>
       </c>
       <c r="H7" t="n">
         <v>390</v>
@@ -661,7 +675,10 @@
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>50550</v>
+        <v>50100</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4410</v>
       </c>
     </row>
     <row r="8">
@@ -684,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>10260</v>
+        <v>10170</v>
       </c>
       <c r="H8" t="n">
         <v>90</v>
@@ -699,7 +716,10 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>19020</v>
+        <v>18960</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1380</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2880</v>
+        <v>2700</v>
       </c>
       <c r="H9" t="n">
         <v>120</v>
@@ -737,7 +757,10 @@
         <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>7410</v>
+        <v>7380</v>
+      </c>
+      <c r="M9" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="10">
@@ -777,6 +800,9 @@
       <c r="L10" t="n">
         <v>4260</v>
       </c>
+      <c r="M10" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -815,6 +841,9 @@
       <c r="L11" t="n">
         <v>2010</v>
       </c>
+      <c r="M11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -853,6 +882,9 @@
       <c r="L12" t="n">
         <v>420</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>240</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>570</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>28530</v>
+        <v>28590</v>
       </c>
       <c r="H4" t="n">
         <v>2580</v>
@@ -1479,7 +1556,10 @@
         <v>44</v>
       </c>
       <c r="L4" t="n">
-        <v>72900</v>
+        <v>72960</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8100</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>4217.85</v>
+        <v>4217.76</v>
       </c>
       <c r="C5" t="n">
         <v>491400</v>
@@ -1502,7 +1582,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>15990</v>
+        <v>16020</v>
       </c>
       <c r="H5" t="n">
         <v>2130</v>
@@ -1517,7 +1597,10 @@
         <v>28</v>
       </c>
       <c r="L5" t="n">
-        <v>44250</v>
+        <v>44310</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8670</v>
       </c>
     </row>
     <row r="6">
@@ -1555,7 +1638,10 @@
         <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>22890</v>
+        <v>22920</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3210</v>
       </c>
     </row>
     <row r="7">
@@ -1595,6 +1681,9 @@
       <c r="L7" t="n">
         <v>9720</v>
       </c>
+      <c r="M7" t="n">
+        <v>1980</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1633,6 +1722,9 @@
       <c r="L8" t="n">
         <v>3000</v>
       </c>
+      <c r="M8" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1671,6 +1763,9 @@
       <c r="L9" t="n">
         <v>960</v>
       </c>
+      <c r="M9" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1804,9 @@
       <c r="L10" t="n">
         <v>660</v>
       </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,7 +1843,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1140</v>
+        <v>1170</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1785,6 +1886,9 @@
       <c r="L12" t="n">
         <v>240</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1898.03</v>
+        <v>1897.99</v>
       </c>
       <c r="C5" t="n">
         <v>270270</v>
@@ -2440,16 +2592,19 @@
         <v>766.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.76</v>
+        <v>9.27</v>
       </c>
       <c r="L5" t="n">
-        <v>9292.5</v>
+        <v>9305.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>173.4</v>
       </c>
     </row>
     <row r="6">
@@ -2484,10 +2639,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9.75</v>
+        <v>7.6</v>
       </c>
       <c r="L6" t="n">
-        <v>8469.299999999999</v>
+        <v>8480.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>256.8</v>
       </c>
     </row>
     <row r="7">
@@ -2522,10 +2680,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>5832</v>
+      </c>
+      <c r="M7" t="n">
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -2565,6 +2726,9 @@
       <c r="L8" t="n">
         <v>2130</v>
       </c>
+      <c r="M8" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>777.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -2641,6 +2808,9 @@
       <c r="L10" t="n">
         <v>587.4</v>
       </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2677,7 +2847,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1140</v>
+        <v>1170</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2717,6 +2890,9 @@
       <c r="L12" t="n">
         <v>240</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2755,6 +2931,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2831,6 +3013,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>4175671.5</v>
+        <v>4175582.4</v>
       </c>
       <c r="C5" t="n">
-        <v>14864850</v>
+        <v>11351340</v>
       </c>
       <c r="D5" t="n">
-        <v>12949882.8</v>
+        <v>24537427.2</v>
       </c>
       <c r="E5" t="n">
-        <v>2633688.69</v>
+        <v>4931733.6</v>
       </c>
       <c r="F5" t="n">
         <v>3333.36</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>212135.22</v>
+        <v>4370760</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>250887.84</v>
+        <v>450017.01</v>
       </c>
       <c r="L5" t="n">
-        <v>87535.35000000001</v>
+        <v>1674918</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52020</v>
       </c>
     </row>
     <row r="6">
@@ -3392,22 +3619,22 @@
         <v>7839532.8</v>
       </c>
       <c r="C6" t="n">
-        <v>13846140</v>
+        <v>10573416</v>
       </c>
       <c r="D6" t="n">
-        <v>11291045.85</v>
+        <v>21394264.32</v>
       </c>
       <c r="E6" t="n">
-        <v>2129740.7</v>
+        <v>3988062</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>9185.25</v>
+        <v>26811</v>
       </c>
       <c r="H6" t="n">
-        <v>520378.65</v>
+        <v>10721700</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3416,10 +3643,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>208006.5</v>
+        <v>369268.38</v>
       </c>
       <c r="L6" t="n">
-        <v>79780.81</v>
+        <v>1526472</v>
+      </c>
+      <c r="M6" t="n">
+        <v>77040</v>
       </c>
     </row>
     <row r="7">
@@ -3430,22 +3660,22 @@
         <v>7509892.5</v>
       </c>
       <c r="C7" t="n">
-        <v>6819120</v>
+        <v>5207328</v>
       </c>
       <c r="D7" t="n">
-        <v>6297802.17</v>
+        <v>11933070.34</v>
       </c>
       <c r="E7" t="n">
-        <v>1058071.9</v>
+        <v>1981300.5</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>10073.25</v>
+        <v>29403</v>
       </c>
       <c r="H7" t="n">
-        <v>18175.9</v>
+        <v>374490</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3454,10 +3684,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>52481.64</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>54937.44</v>
+        <v>1049760</v>
+      </c>
+      <c r="M7" t="n">
+        <v>207900</v>
       </c>
     </row>
     <row r="8">
@@ -3468,22 +3701,22 @@
         <v>4958712</v>
       </c>
       <c r="C8" t="n">
-        <v>2772000</v>
+        <v>2116800</v>
       </c>
       <c r="D8" t="n">
-        <v>2953323.65</v>
+        <v>5595955.2</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>456993.9</v>
       </c>
       <c r="F8" t="n">
         <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>58441.5</v>
+        <v>170586</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3495,7 +3728,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20064.6</v>
+        <v>383400</v>
+      </c>
+      <c r="M8" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>2137806</v>
       </c>
       <c r="C9" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D9" t="n">
-        <v>837764.83</v>
+        <v>1587396.1</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13680.75</v>
+        <v>39933</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>64002</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>7324.99</v>
+        <v>139968</v>
+      </c>
+      <c r="M9" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>961290</v>
       </c>
       <c r="C10" t="n">
-        <v>443520</v>
+        <v>338688</v>
       </c>
       <c r="D10" t="n">
-        <v>558563.39</v>
+        <v>1058365.44</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3571,7 +3810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5533.31</v>
+        <v>105732</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,10 +3824,10 @@
         <v>646272</v>
       </c>
       <c r="C11" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D11" t="n">
-        <v>612914.97</v>
+        <v>1161350.78</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3594,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3609,7 +3851,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10738.8</v>
+        <v>210600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3620,10 +3865,10 @@
         <v>534996</v>
       </c>
       <c r="C12" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D12" t="n">
-        <v>297579.46</v>
+        <v>563853.3100000001</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3632,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3647,7 +3892,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3658,10 +3906,10 @@
         <v>628056</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3673,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3685,7 +3933,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>702900</v>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D14" t="n">
-        <v>156012.53</v>
+        <v>295612.42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3723,6 +3974,9 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3734,10 +3988,10 @@
         <v>277398</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3761,6 +4015,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3772,10 +4029,10 @@
         <v>212454</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,6 +4056,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3839,6 +4099,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>13680</v>
+        <v>13740</v>
       </c>
       <c r="H4" t="n">
         <v>930</v>
@@ -4275,7 +4568,10 @@
         <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>46800</v>
+        <v>46890</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4313,7 +4609,10 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>7680</v>
+        <v>7710</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>1230</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>270</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.26</v>
+        <v>0.99</v>
       </c>
       <c r="L5" t="n">
-        <v>1612.8</v>
+        <v>1619.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>455.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>162</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>415116.9</v>
       </c>
       <c r="C5" t="n">
-        <v>2195424</v>
+        <v>1676505.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1912598.08</v>
+        <v>3623989.25</v>
       </c>
       <c r="E5" t="n">
-        <v>237763.56</v>
+        <v>445225.95</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>23902.56</v>
+        <v>492480</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>26880.84</v>
+        <v>48216.11</v>
       </c>
       <c r="L5" t="n">
-        <v>15192.58</v>
+        <v>291438</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,19 +6631,19 @@
         <v>58449.6</v>
       </c>
       <c r="C6" t="n">
-        <v>798336</v>
+        <v>609638.4</v>
       </c>
       <c r="D6" t="n">
-        <v>651015.26</v>
+        <v>1233543.17</v>
       </c>
       <c r="E6" t="n">
-        <v>28022.9</v>
+        <v>52474.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>416.25</v>
+        <v>1215</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>4287.04</v>
+        <v>81918</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,13 +6672,13 @@
         <v>31977</v>
       </c>
       <c r="C7" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D7" t="n">
-        <v>51201.64</v>
+        <v>97016.83</v>
       </c>
       <c r="E7" t="n">
-        <v>35269.06</v>
+        <v>66043.35000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1526.04</v>
+        <v>29160</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>360.75</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,6 +6740,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6331,6 +6783,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7072,6 +7581,9 @@
       </c>
       <c r="L4" t="n">
         <v>14610</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>4320</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>300</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>30</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="L5" t="n">
         <v>907.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>111</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>753875.1</v>
       </c>
       <c r="C5" t="n">
-        <v>2530836</v>
+        <v>1932638.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2204800.56</v>
+        <v>4177654.27</v>
       </c>
       <c r="E5" t="n">
-        <v>109737.03</v>
+        <v>205488.9</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>80671.14</v>
+        <v>1662120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>44801.4</v>
+        <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>8545.82</v>
+        <v>163296</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,19 +9643,19 @@
         <v>241876.8</v>
       </c>
       <c r="C6" t="n">
-        <v>898128</v>
+        <v>685843.2</v>
       </c>
       <c r="D6" t="n">
-        <v>732392.16</v>
+        <v>1387736.06</v>
       </c>
       <c r="E6" t="n">
-        <v>56045.81</v>
+        <v>104949</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>915.75</v>
+        <v>2673</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1045.62</v>
+        <v>19980</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9034,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>416.25</v>
+        <v>1215</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17493.88</v>
+        <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>169.56</v>
+        <v>3240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,10 +9725,10 @@
         <v>7128</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>89850</v>
+        <v>89910</v>
       </c>
       <c r="H4" t="n">
-        <v>15240</v>
+        <v>15150</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -9864,10 +10589,13 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L4" t="n">
-        <v>215400</v>
+        <v>215520</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12150</v>
       </c>
     </row>
     <row r="5">
@@ -9890,10 +10618,10 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>28830</v>
+        <v>28890</v>
       </c>
       <c r="H5" t="n">
-        <v>3570</v>
+        <v>3600</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -9905,7 +10633,10 @@
         <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>91620</v>
+        <v>91680</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4710</v>
       </c>
     </row>
     <row r="6">
@@ -9945,6 +10676,9 @@
       <c r="L6" t="n">
         <v>29070</v>
       </c>
+      <c r="M6" t="n">
+        <v>2580</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9983,6 +10717,9 @@
       <c r="L7" t="n">
         <v>11430</v>
       </c>
+      <c r="M7" t="n">
+        <v>840</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>4320</v>
       </c>
+      <c r="M8" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>3120</v>
       </c>
+      <c r="M9" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>2190</v>
       </c>
+      <c r="M10" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>480</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>90</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>30</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>23677.19</v>
+        <v>23665.65</v>
       </c>
       <c r="C5" t="n">
         <v>3072207.6</v>
@@ -10828,16 +11628,19 @@
         <v>4417.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>86.94</v>
+        <v>65.87</v>
       </c>
       <c r="L5" t="n">
-        <v>71347.5</v>
+        <v>71145.89999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>406.8</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>17307.79</v>
+        <v>17306.93</v>
       </c>
       <c r="C6" t="n">
         <v>1445623.2</v>
@@ -10860,7 +11663,7 @@
         <v>0.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2226</v>
+        <v>2208</v>
       </c>
       <c r="H6" t="n">
         <v>2462.4</v>
@@ -10872,10 +11675,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>30.55</v>
+        <v>23.32</v>
       </c>
       <c r="L6" t="n">
-        <v>39571.5</v>
+        <v>39338.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>621.6</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>12454.96</v>
+        <v>12454.87</v>
       </c>
       <c r="C7" t="n">
         <v>598248</v>
@@ -10898,7 +11704,7 @@
         <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2628</v>
+        <v>2583</v>
       </c>
       <c r="H7" t="n">
         <v>284.7</v>
@@ -10910,10 +11716,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>9.84</v>
+        <v>7.66</v>
       </c>
       <c r="L7" t="n">
-        <v>30330</v>
+        <v>30060</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1543.5</v>
       </c>
     </row>
     <row r="8">
@@ -10936,7 +11745,7 @@
         <v>2.85</v>
       </c>
       <c r="G8" t="n">
-        <v>6669</v>
+        <v>6610.5</v>
       </c>
       <c r="H8" t="n">
         <v>76.5</v>
@@ -10948,10 +11757,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
-        <v>13504.2</v>
+        <v>13461.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>828</v>
       </c>
     </row>
     <row r="9">
@@ -10974,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2448</v>
+        <v>2295</v>
       </c>
       <c r="H9" t="n">
         <v>120</v>
@@ -10986,10 +11798,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4.82</v>
       </c>
       <c r="L9" t="n">
-        <v>6002.1</v>
+        <v>5977.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="10">
@@ -11029,6 +11844,9 @@
       <c r="L10" t="n">
         <v>3791.4</v>
       </c>
+      <c r="M10" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11067,6 +11885,9 @@
       <c r="L11" t="n">
         <v>2010</v>
       </c>
+      <c r="M11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -11105,6 +11926,9 @@
       <c r="L12" t="n">
         <v>420</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -11143,6 +11967,9 @@
       <c r="L13" t="n">
         <v>240</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>570</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11219,6 +12049,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11757,19 +12629,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1285.2</v>
+        <v>1296</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>25.2</v>
+        <v>19.86</v>
       </c>
       <c r="L5" t="n">
-        <v>19240.2</v>
+        <v>19252.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>94.2</v>
       </c>
     </row>
     <row r="6">
@@ -11804,10 +12679,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7.8</v>
+        <v>6.08</v>
       </c>
       <c r="L6" t="n">
         <v>10755.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>206.4</v>
       </c>
     </row>
     <row r="7">
@@ -11842,10 +12720,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>6858</v>
+      </c>
+      <c r="M7" t="n">
+        <v>294</v>
       </c>
     </row>
     <row r="8">
@@ -11885,6 +12766,9 @@
       <c r="L8" t="n">
         <v>3067.2</v>
       </c>
+      <c r="M8" t="n">
+        <v>198</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -11923,6 +12807,9 @@
       <c r="L9" t="n">
         <v>2527.2</v>
       </c>
+      <c r="M9" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>1949.1</v>
       </c>
+      <c r="M10" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>480</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>90</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>30</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>17225881.2</v>
       </c>
       <c r="C5" t="n">
-        <v>39868290</v>
+        <v>30444876</v>
       </c>
       <c r="D5" t="n">
-        <v>34732249.77</v>
+        <v>65810638.08</v>
       </c>
       <c r="E5" t="n">
-        <v>2780004.73</v>
+        <v>5205718.8</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>355550.58</v>
+        <v>7387200</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>69999.60000000001</v>
+        <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>537616.8</v>
+        <v>964322.16</v>
       </c>
       <c r="L5" t="n">
-        <v>181242.68</v>
+        <v>3465504</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28260</v>
       </c>
     </row>
     <row r="6">
@@ -12712,22 +13659,22 @@
         <v>5011459.2</v>
       </c>
       <c r="C6" t="n">
-        <v>11276496</v>
+        <v>8611142.4</v>
       </c>
       <c r="D6" t="n">
-        <v>9195590.5</v>
+        <v>17423797.25</v>
       </c>
       <c r="E6" t="n">
-        <v>84068.71000000001</v>
+        <v>157423.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5994</v>
+        <v>17496</v>
       </c>
       <c r="H6" t="n">
-        <v>75691.44</v>
+        <v>1559520</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12736,10 +13683,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>166405.2</v>
+        <v>295414.7</v>
       </c>
       <c r="L6" t="n">
-        <v>101320.58</v>
+        <v>1936062</v>
+      </c>
+      <c r="M6" t="n">
+        <v>61920</v>
       </c>
     </row>
     <row r="7">
@@ -12750,19 +13700,19 @@
         <v>2716540.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2661120</v>
+        <v>2032128</v>
       </c>
       <c r="D7" t="n">
-        <v>2457678.9</v>
+        <v>4656807.94</v>
       </c>
       <c r="E7" t="n">
-        <v>35269.06</v>
+        <v>66043.35000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -12774,10 +13724,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>69975.52</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>64602.36</v>
+        <v>1234440</v>
+      </c>
+      <c r="M7" t="n">
+        <v>88200</v>
       </c>
     </row>
     <row r="8">
@@ -12788,10 +13741,10 @@
         <v>308286</v>
       </c>
       <c r="C8" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D8" t="n">
-        <v>177199.42</v>
+        <v>335757.31</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -12800,7 +13753,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6493.5</v>
+        <v>18954</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12815,7 +13768,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>28893.02</v>
+        <v>552096</v>
+      </c>
+      <c r="M8" t="n">
+        <v>59400</v>
       </c>
     </row>
     <row r="9">
@@ -12826,10 +13782,10 @@
         <v>219780</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -12838,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3774</v>
+        <v>11016</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -12853,7 +13809,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>23806.22</v>
+        <v>454896</v>
+      </c>
+      <c r="M9" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,10 +13823,10 @@
         <v>110088</v>
       </c>
       <c r="C10" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D10" t="n">
-        <v>209461.27</v>
+        <v>396887.04</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12876,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4995</v>
+        <v>14580</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>18360.52</v>
+        <v>350838</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,10 +13864,10 @@
         <v>28116</v>
       </c>
       <c r="C11" t="n">
-        <v>277200</v>
+        <v>211680</v>
       </c>
       <c r="D11" t="n">
-        <v>360538.22</v>
+        <v>683147.52</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12914,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>66600</v>
+        <v>194400</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4521.6</v>
+        <v>86400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -12940,10 +13905,10 @@
         <v>13266</v>
       </c>
       <c r="C12" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D12" t="n">
-        <v>37197.43</v>
+        <v>70481.66</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12952,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>6732</v>
       </c>
       <c r="C13" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D13" t="n">
-        <v>114300.85</v>
+        <v>216577.15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13005,6 +13973,9 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13081,6 +14055,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13121,6 +14098,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -13159,6 +14139,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -13168,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13195,6 +14178,9 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13206,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D19" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13233,6 +14219,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13273,6 +14262,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D22" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13387,6 +14385,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13425,6 +14426,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>28920</v>
+        <v>28980</v>
       </c>
       <c r="H4" t="n">
         <v>2670</v>
@@ -13595,7 +14608,10 @@
         <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>111750</v>
+        <v>112770</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3840</v>
+        <v>3900</v>
       </c>
       <c r="H5" t="n">
         <v>360</v>
@@ -13633,7 +14649,10 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>24480</v>
+        <v>24090</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4500</v>
+        <v>4920</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>180</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>60</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>180</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>90</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="L5" t="n">
-        <v>5140.8</v>
+        <v>5058.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1665</v>
+        <v>1820.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>108</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>42.6</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>145.8</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>80.09999999999999</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>1194029.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4284126</v>
+        <v>3271514.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3732222.63</v>
+        <v>7071812.35</v>
       </c>
       <c r="E5" t="n">
-        <v>859606.73</v>
+        <v>1609663.05</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>35853.84</v>
+        <v>738720</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>17920.56</v>
+        <v>32144.07</v>
       </c>
       <c r="L5" t="n">
-        <v>48426.34</v>
+        <v>910602</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,19 +16671,19 @@
         <v>235224</v>
       </c>
       <c r="C6" t="n">
-        <v>573804</v>
+        <v>438177.6</v>
       </c>
       <c r="D6" t="n">
-        <v>467917.22</v>
+        <v>886609.15</v>
       </c>
       <c r="E6" t="n">
-        <v>84068.71000000001</v>
+        <v>157423.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>222</v>
+        <v>648</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15684.3</v>
+        <v>327672</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,10 +16712,10 @@
         <v>85021.2</v>
       </c>
       <c r="C7" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D7" t="n">
-        <v>25600.82</v>
+        <v>48508.42</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15558,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1017.36</v>
+        <v>19440</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>360.75</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>401.29</v>
+        <v>7668</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1373.44</v>
+        <v>26244</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>754.54</v>
+        <v>14418</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15727,6 +16905,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>52089820.2</v>
+        <v>52064426.7</v>
       </c>
       <c r="C5" t="n">
-        <v>168971418</v>
+        <v>129032719.2</v>
       </c>
       <c r="D5" t="n">
-        <v>147203642.16</v>
+        <v>278921339.14</v>
       </c>
       <c r="E5" t="n">
-        <v>17228713.52</v>
+        <v>32261757.3</v>
       </c>
       <c r="F5" t="n">
         <v>23333.52</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1222018.38</v>
+        <v>25178040</v>
       </c>
       <c r="I5" t="n">
-        <v>229998</v>
+        <v>257152.58</v>
       </c>
       <c r="J5" t="n">
-        <v>139999.2</v>
+        <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1854777.96</v>
+        <v>3198335.16</v>
       </c>
       <c r="L5" t="n">
-        <v>672093.45</v>
+        <v>12806262</v>
+      </c>
+      <c r="M5" t="n">
+        <v>122040</v>
       </c>
     </row>
     <row r="6">
@@ -16437,25 +17672,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>38077142.4</v>
+        <v>38075241.6</v>
       </c>
       <c r="C6" t="n">
-        <v>79509276</v>
+        <v>60716174.4</v>
       </c>
       <c r="D6" t="n">
-        <v>64837050.68</v>
+        <v>122853189.89</v>
       </c>
       <c r="E6" t="n">
-        <v>7117817.62</v>
+        <v>13328523</v>
       </c>
       <c r="F6" t="n">
         <v>33333.6</v>
       </c>
       <c r="G6" t="n">
-        <v>41181</v>
+        <v>119232</v>
       </c>
       <c r="H6" t="n">
-        <v>681222.96</v>
+        <v>14035680</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -16464,10 +17699,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>651753.7</v>
+        <v>1132423.03</v>
       </c>
       <c r="L6" t="n">
-        <v>372763.53</v>
+        <v>7080912</v>
+      </c>
+      <c r="M6" t="n">
+        <v>186480</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>27400903.2</v>
+        <v>27400715.1</v>
       </c>
       <c r="C7" t="n">
-        <v>32903640</v>
+        <v>25126416</v>
       </c>
       <c r="D7" t="n">
-        <v>30388175.52</v>
+        <v>57579489.79</v>
       </c>
       <c r="E7" t="n">
-        <v>3103677.56</v>
+        <v>5811814.8</v>
       </c>
       <c r="F7" t="n">
         <v>100000.8</v>
       </c>
       <c r="G7" t="n">
-        <v>48618</v>
+        <v>139482</v>
       </c>
       <c r="H7" t="n">
-        <v>78762.25</v>
+        <v>1622790</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>209926.56</v>
+        <v>371744.74</v>
       </c>
       <c r="L7" t="n">
-        <v>285708.6</v>
+        <v>5410800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>463050</v>
       </c>
     </row>
     <row r="8">
@@ -16516,22 +17757,22 @@
         <v>15921576</v>
       </c>
       <c r="C8" t="n">
-        <v>10783080</v>
+        <v>8234352</v>
       </c>
       <c r="D8" t="n">
-        <v>11488428.99</v>
+        <v>21768265.73</v>
       </c>
       <c r="E8" t="n">
-        <v>1179565.28</v>
+        <v>2208803.85</v>
       </c>
       <c r="F8" t="n">
         <v>118750.95</v>
       </c>
       <c r="G8" t="n">
-        <v>123376.5</v>
+        <v>356967</v>
       </c>
       <c r="H8" t="n">
-        <v>21163.72</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16540,10 +17781,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>76802.39999999999</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>127209.56</v>
+        <v>2423088</v>
+      </c>
+      <c r="M8" t="n">
+        <v>248400</v>
       </c>
     </row>
     <row r="9">
@@ -16554,22 +17798,22 @@
         <v>8271450</v>
       </c>
       <c r="C9" t="n">
-        <v>4268880</v>
+        <v>3259872</v>
       </c>
       <c r="D9" t="n">
-        <v>4962145.5</v>
+        <v>9402269.18</v>
       </c>
       <c r="E9" t="n">
-        <v>843389.92</v>
+        <v>1579296.15</v>
       </c>
       <c r="F9" t="n">
         <v>41667</v>
       </c>
       <c r="G9" t="n">
-        <v>45288</v>
+        <v>123930</v>
       </c>
       <c r="H9" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16578,10 +17822,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>128004</v>
+        <v>233942.81</v>
       </c>
       <c r="L9" t="n">
-        <v>56539.78</v>
+        <v>1076004</v>
+      </c>
+      <c r="M9" t="n">
+        <v>135000</v>
       </c>
     </row>
     <row r="10">
@@ -16592,22 +17839,22 @@
         <v>4260762</v>
       </c>
       <c r="C10" t="n">
-        <v>1441440</v>
+        <v>1100736</v>
       </c>
       <c r="D10" t="n">
-        <v>1815331</v>
+        <v>3439687.68</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>18870</v>
+        <v>55080</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16619,7 +17866,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>35714.99</v>
+        <v>682452</v>
+      </c>
+      <c r="M10" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,19 +17880,19 @@
         <v>2524302</v>
       </c>
       <c r="C11" t="n">
-        <v>1275120</v>
+        <v>973728</v>
       </c>
       <c r="D11" t="n">
-        <v>1658475.81</v>
+        <v>3142478.59</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>72705</v>
+        <v>212220</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -16657,7 +17907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>18934.2</v>
+        <v>361800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,22 +17921,22 @@
         <v>1892880</v>
       </c>
       <c r="C12" t="n">
-        <v>526680</v>
+        <v>402192</v>
       </c>
       <c r="D12" t="n">
-        <v>706751.21</v>
+        <v>1339151.62</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>41667</v>
       </c>
       <c r="G12" t="n">
-        <v>4995</v>
+        <v>14580</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16695,7 +17948,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3956.4</v>
+        <v>75600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -16706,10 +17962,10 @@
         <v>1888326</v>
       </c>
       <c r="C13" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D13" t="n">
-        <v>533403.96</v>
+        <v>1010693.38</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16718,10 +17974,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16733,7 +17989,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -16744,10 +18003,10 @@
         <v>1930698</v>
       </c>
       <c r="C14" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D14" t="n">
-        <v>273021.93</v>
+        <v>517321.73</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16756,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>22680</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5369.4</v>
+        <v>102600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -16782,10 +18044,10 @@
         <v>820116</v>
       </c>
       <c r="C15" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D15" t="n">
-        <v>276954.35</v>
+        <v>524772.86</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16809,6 +18071,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16820,10 +18085,10 @@
         <v>308682</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16847,6 +18112,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16887,6 +18155,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -16896,10 +18167,10 @@
         <v>6534</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16923,6 +18194,9 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16934,10 +18208,10 @@
         <v>396</v>
       </c>
       <c r="C19" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D19" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16961,6 +18235,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17001,6 +18278,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D22" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17115,6 +18401,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -17153,6 +18442,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>27884.07</v>
+        <v>27809.55</v>
       </c>
       <c r="C4" t="n">
         <v>2970576</v>
@@ -17308,7 +18609,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>77940</v>
+        <v>76020</v>
       </c>
       <c r="H4" t="n">
         <v>3750</v>
@@ -17320,10 +18621,13 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="L4" t="n">
-        <v>178110</v>
+        <v>174570</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16590</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13967.1</v>
+        <v>13951.71</v>
       </c>
       <c r="C5" t="n">
         <v>1009512</v>
@@ -17346,7 +18650,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>35550</v>
+        <v>35040</v>
       </c>
       <c r="H5" t="n">
         <v>600</v>
@@ -17358,10 +18662,13 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="L5" t="n">
-        <v>69120</v>
+        <v>68190</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3600</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6191.55</v>
+        <v>6190.47</v>
       </c>
       <c r="C6" t="n">
         <v>308952</v>
@@ -17384,7 +18691,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>14970</v>
+        <v>14550</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -17396,10 +18703,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
-        <v>21720</v>
+        <v>21120</v>
+      </c>
+      <c r="M6" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2435.85</v>
+        <v>2435.76</v>
       </c>
       <c r="C7" t="n">
         <v>98784</v>
@@ -17422,7 +18732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4950</v>
+        <v>4710</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -17437,7 +18747,10 @@
         <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>8820</v>
+        <v>8370</v>
+      </c>
+      <c r="M7" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -17460,7 +18773,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1290</v>
+        <v>1200</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -17475,7 +18788,10 @@
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>2670</v>
+        <v>2610</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>570</v>
+        <v>390</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -17513,7 +18829,10 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>1110</v>
+        <v>1080</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -17553,6 +18872,9 @@
       <c r="L10" t="n">
         <v>360</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -17591,6 +18913,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -17629,6 +18954,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>6285.2</v>
+        <v>6278.27</v>
       </c>
       <c r="C5" t="n">
         <v>555231.6</v>
@@ -18290,10 +19666,13 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>26.46</v>
+        <v>18.21</v>
       </c>
       <c r="L5" t="n">
-        <v>14515.2</v>
+        <v>14319.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4953.24</v>
+        <v>4952.38</v>
       </c>
       <c r="C6" t="n">
         <v>278056.8</v>
@@ -18316,7 +19695,7 @@
         <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>748.5</v>
+        <v>727.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -18328,10 +19707,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8.449999999999999</v>
+        <v>6.08</v>
       </c>
       <c r="L6" t="n">
-        <v>8036.4</v>
+        <v>7814.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2314.06</v>
+        <v>2313.97</v>
       </c>
       <c r="C7" t="n">
         <v>98784</v>
@@ -18354,7 +19736,7 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>742.5</v>
+        <v>706.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -18366,10 +19748,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
-        <v>5292</v>
+        <v>5022</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -18392,7 +19777,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>838.5</v>
+        <v>780</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -18404,10 +19789,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
-        <v>1895.7</v>
+        <v>1853.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>484.5</v>
+        <v>331.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -18442,10 +19830,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>899.1</v>
+        <v>874.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -18485,6 +19876,9 @@
       <c r="L10" t="n">
         <v>320.4</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -18523,6 +19917,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -18561,6 +19958,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -18599,6 +19999,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13827429</v>
+        <v>13812192.9</v>
       </c>
       <c r="C5" t="n">
-        <v>30537738</v>
+        <v>23319727.2</v>
       </c>
       <c r="D5" t="n">
-        <v>26603707.95</v>
+        <v>50408683.78</v>
       </c>
       <c r="E5" t="n">
-        <v>4151717.59</v>
+        <v>7774330.05</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>59756.4</v>
+        <v>1231200</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>34999.8</v>
+        <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>564497.64</v>
+        <v>883961.98</v>
       </c>
       <c r="L5" t="n">
-        <v>136733.18</v>
+        <v>2577582</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21600</v>
       </c>
     </row>
     <row r="6">
@@ -19233,22 +20684,22 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>10897128</v>
+        <v>10895227.2</v>
       </c>
       <c r="C6" t="n">
-        <v>15293124</v>
+        <v>11678385.6</v>
       </c>
       <c r="D6" t="n">
-        <v>12471011</v>
+        <v>23630061.31</v>
       </c>
       <c r="E6" t="n">
-        <v>1877534.57</v>
+        <v>3515791.5</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>13847.25</v>
+        <v>39285</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -19260,10 +20711,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>180272.3</v>
+        <v>295414.7</v>
       </c>
       <c r="L6" t="n">
-        <v>75702.89</v>
+        <v>1406592</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5760</v>
       </c>
     </row>
     <row r="7">
@@ -19271,22 +20725,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5090926.5</v>
+        <v>5090738.4</v>
       </c>
       <c r="C7" t="n">
-        <v>5433120</v>
+        <v>4148928</v>
       </c>
       <c r="D7" t="n">
-        <v>5017761.08</v>
+        <v>9507649.539999999</v>
       </c>
       <c r="E7" t="n">
-        <v>916995.64</v>
+        <v>1717127.1</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13736.25</v>
+        <v>38151</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -19295,13 +20749,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>69975.52</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>49850.64</v>
+        <v>903960</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6300</v>
       </c>
     </row>
     <row r="8">
@@ -19312,19 +20769,19 @@
         <v>2399958</v>
       </c>
       <c r="C8" t="n">
-        <v>1330560</v>
+        <v>1016064</v>
       </c>
       <c r="D8" t="n">
-        <v>1417595.35</v>
+        <v>2686058.5</v>
       </c>
       <c r="E8" t="n">
-        <v>528770.64</v>
+        <v>990153.45</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>15512.25</v>
+        <v>42120</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -19336,10 +20793,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57601.8</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>17857.49</v>
+        <v>333558</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>836352</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>740880</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>2136879.36</v>
       </c>
       <c r="E9" t="n">
-        <v>443889.43</v>
+        <v>831208.5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8963.25</v>
+        <v>17901</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19374,10 +20834,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>42668</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>8469.52</v>
+        <v>157464</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -19388,10 +20851,10 @@
         <v>408672</v>
       </c>
       <c r="C10" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D10" t="n">
-        <v>488742.96</v>
+        <v>926069.76</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -19400,7 +20863,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -19415,7 +20878,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3018.17</v>
+        <v>57672</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -19426,10 +20892,10 @@
         <v>217404</v>
       </c>
       <c r="C11" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D11" t="n">
-        <v>144215.29</v>
+        <v>273259.01</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19453,7 +20919,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -19464,13 +20933,13 @@
         <v>125928</v>
       </c>
       <c r="C12" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D12" t="n">
-        <v>185987.16</v>
+        <v>352408.32</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -19491,6 +20960,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19502,10 +20974,10 @@
         <v>74448</v>
       </c>
       <c r="C13" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D13" t="n">
-        <v>114300.85</v>
+        <v>216577.15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19514,7 +20986,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19529,6 +21001,9 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19569,6 +21044,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -19607,6 +21085,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -19645,6 +21126,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -19683,6 +21167,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19949,6 +21454,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>86340</v>
+        <v>86430</v>
       </c>
       <c r="H4" t="n">
-        <v>29070</v>
+        <v>29100</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -20119,7 +21636,10 @@
         <v>148</v>
       </c>
       <c r="L4" t="n">
-        <v>240780</v>
+        <v>240270</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,10 +21662,10 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>28110</v>
+        <v>28320</v>
       </c>
       <c r="H5" t="n">
-        <v>3330</v>
+        <v>3390</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20157,7 +21677,10 @@
         <v>44</v>
       </c>
       <c r="L5" t="n">
-        <v>62820</v>
+        <v>63570</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20195,7 +21718,10 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>7440</v>
+        <v>7110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20218,7 +21744,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="H7" t="n">
         <v>300</v>
@@ -20234,6 +21760,9 @@
       </c>
       <c r="L7" t="n">
         <v>2850</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20273,6 +21802,9 @@
       <c r="L8" t="n">
         <v>540</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -20311,6 +21843,9 @@
       <c r="L9" t="n">
         <v>180</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>30</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21077,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1198.8</v>
+        <v>1220.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21086,10 +22678,13 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>18.48</v>
+        <v>14.56</v>
       </c>
       <c r="L5" t="n">
-        <v>13192.2</v>
+        <v>13349.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21124,10 +22719,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="L6" t="n">
-        <v>2752.8</v>
+        <v>2630.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21150,7 +22748,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>40.5</v>
+        <v>45</v>
       </c>
       <c r="H7" t="n">
         <v>219</v>
@@ -21166,6 +22764,9 @@
       </c>
       <c r="L7" t="n">
         <v>1710</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21205,6 +22806,9 @@
       <c r="L8" t="n">
         <v>383.4</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -21243,6 +22847,9 @@
       <c r="L9" t="n">
         <v>145.8</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>26.7</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>6874688.7</v>
       </c>
       <c r="C5" t="n">
-        <v>21313908</v>
+        <v>16276075.2</v>
       </c>
       <c r="D5" t="n">
-        <v>18568139.65</v>
+        <v>35182895.62</v>
       </c>
       <c r="E5" t="n">
-        <v>1554607.91</v>
+        <v>2911092.75</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>331648.02</v>
+        <v>6956280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>34999.8</v>
+        <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>394252.32</v>
+        <v>707169.58</v>
       </c>
       <c r="L5" t="n">
-        <v>124270.52</v>
+        <v>2402946</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,22 +23699,22 @@
         <v>632016</v>
       </c>
       <c r="C6" t="n">
-        <v>4839912</v>
+        <v>3695932.8</v>
       </c>
       <c r="D6" t="n">
-        <v>3946779.99</v>
+        <v>7478355.46</v>
       </c>
       <c r="E6" t="n">
-        <v>252206.14</v>
+        <v>472270.5</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>804.75</v>
+        <v>2349</v>
       </c>
       <c r="H6" t="n">
-        <v>85152.87</v>
+        <v>1754460</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22056,10 +23723,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>55468.4</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>25931.38</v>
+        <v>473526</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,10 +23740,10 @@
         <v>123957.9</v>
       </c>
       <c r="C7" t="n">
-        <v>665280</v>
+        <v>508032</v>
       </c>
       <c r="D7" t="n">
-        <v>614419.72</v>
+        <v>1164201.98</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -22082,10 +23752,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>749.25</v>
+        <v>2430</v>
       </c>
       <c r="H7" t="n">
-        <v>60586.35</v>
+        <v>1248300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22097,7 +23767,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16108.2</v>
+        <v>307800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>52470</v>
       </c>
       <c r="C8" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D8" t="n">
-        <v>88599.71000000001</v>
+        <v>167878.66</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22120,10 +23793,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>360.75</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
-        <v>7054.58</v>
+        <v>145350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3611.63</v>
+        <v>69012</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22161,7 +23837,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1373.44</v>
+        <v>26244</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>251.51</v>
+        <v>4806</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22251,6 +23933,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>662</v>
+        <v>227</v>
       </c>
       <c r="L4" t="n">
         <v>920130</v>
@@ -590,7 +590,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="L5" t="n">
         <v>338790</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>106320</v>
@@ -672,7 +672,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>50100</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>18960</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>7380</v>
@@ -1553,7 +1553,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>72960</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>44310</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>22920</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>9720</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>960</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9.27</v>
+        <v>2.32</v>
       </c>
       <c r="L5" t="n">
         <v>9305.1</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>8480.4</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5832</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>777.6</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>450017.01</v>
+        <v>112504.25</v>
       </c>
       <c r="L5" t="n">
         <v>1674918</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>369268.38</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1526472</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1049760</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>116971.4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>139968</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
         <v>46890</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>7710</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
       <c r="L5" t="n">
         <v>1619.1</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>48216.11</v>
+        <v>16072.04</v>
       </c>
       <c r="L5" t="n">
         <v>291438</v>
@@ -7577,7 +7577,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>14610</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>4320</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>300</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>907.2</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>111</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>80360.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>163296</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>19980</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>30978.73</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3240</v>
@@ -10589,7 +10589,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>229</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
         <v>215520</v>
@@ -10630,7 +10630,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
         <v>91680</v>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>29070</v>
@@ -10712,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>11430</v>
@@ -11634,7 +11634,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>65.87</v>
+        <v>14.23</v>
       </c>
       <c r="L5" t="n">
         <v>71145.89999999999</v>
@@ -11675,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>23.32</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>39338.4</v>
@@ -11716,7 +11716,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>30060</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>13461.6</v>
@@ -11798,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.82</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>5977.8</v>
@@ -12638,7 +12638,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>19.86</v>
+        <v>5.63</v>
       </c>
       <c r="L5" t="n">
         <v>19252.8</v>
@@ -12679,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6.08</v>
+        <v>2.54</v>
       </c>
       <c r="L6" t="n">
         <v>10755.9</v>
@@ -12720,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>6858</v>
@@ -13642,7 +13642,7 @@
         <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>964322.16</v>
+        <v>273224.61</v>
       </c>
       <c r="L5" t="n">
         <v>3465504</v>
@@ -13683,7 +13683,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>295414.7</v>
+        <v>123089.46</v>
       </c>
       <c r="L6" t="n">
         <v>1936062</v>
@@ -13724,7 +13724,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>123914.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1234440</v>
@@ -14605,7 +14605,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
         <v>112770</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>24090</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>5058.9</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>32144.07</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>910602</v>
@@ -17658,7 +17658,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3198335.16</v>
+        <v>691097.55</v>
       </c>
       <c r="L5" t="n">
         <v>12806262</v>
@@ -17699,7 +17699,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1132423.03</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
         <v>7080912</v>
@@ -17740,7 +17740,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>371744.74</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5410800</v>
@@ -17781,7 +17781,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>142948.86</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2423088</v>
@@ -17822,7 +17822,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>233942.81</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
         <v>1076004</v>
@@ -18621,7 +18621,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>174570</v>
@@ -18662,7 +18662,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>68190</v>
@@ -18703,7 +18703,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>21120</v>
@@ -18744,7 +18744,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>8370</v>
@@ -18785,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2610</v>
@@ -18826,7 +18826,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>1080</v>
@@ -19666,7 +19666,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>18.21</v>
+        <v>2.32</v>
       </c>
       <c r="L5" t="n">
         <v>14319.9</v>
@@ -19707,7 +19707,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6.08</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>7814.4</v>
@@ -19748,7 +19748,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5022</v>
@@ -19789,7 +19789,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1853.1</v>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
         <v>874.8</v>
@@ -20670,7 +20670,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>883961.98</v>
+        <v>112504.25</v>
       </c>
       <c r="L5" t="n">
         <v>2577582</v>
@@ -20711,7 +20711,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>295414.7</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1406592</v>
@@ -20752,7 +20752,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>123914.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>903960</v>
@@ -20793,7 +20793,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>107211.65</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>333558</v>
@@ -20834,7 +20834,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>38990.47</v>
       </c>
       <c r="L9" t="n">
         <v>157464</v>
@@ -21633,7 +21633,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="L4" t="n">
         <v>240270</v>
@@ -21674,7 +21674,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>63570</v>
@@ -21715,7 +21715,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>7110</v>
@@ -22678,7 +22678,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>14.56</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>13349.7</v>
@@ -22719,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2630.7</v>
@@ -23682,7 +23682,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>707169.58</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>2402946</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>98471.57000000001</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>473526</v>

--- a/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_5yrs_Future_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>355710</v>
       </c>
       <c r="H4" t="n">
-        <v>59580</v>
+        <v>69960</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -572,22 +572,22 @@
         <v>227</v>
       </c>
       <c r="L4" t="n">
-        <v>920130</v>
+        <v>1130580</v>
       </c>
       <c r="M4" t="n">
-        <v>42570</v>
+        <v>72690</v>
       </c>
       <c r="N4" t="n">
-        <v>39060</v>
+        <v>53850</v>
       </c>
       <c r="O4" t="n">
-        <v>259020</v>
+        <v>318270</v>
       </c>
       <c r="P4" t="n">
-        <v>85230</v>
+        <v>51240</v>
       </c>
       <c r="Q4" t="n">
-        <v>149591.21</v>
+        <v>1550199.2</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>133020</v>
       </c>
       <c r="H5" t="n">
-        <v>12270</v>
+        <v>15660</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -625,22 +625,22 @@
         <v>43</v>
       </c>
       <c r="L5" t="n">
-        <v>338790</v>
+        <v>421530</v>
       </c>
       <c r="M5" t="n">
-        <v>20340</v>
+        <v>49440</v>
       </c>
       <c r="N5" t="n">
-        <v>12570</v>
+        <v>15780</v>
       </c>
       <c r="O5" t="n">
-        <v>106230</v>
+        <v>136590</v>
       </c>
       <c r="P5" t="n">
-        <v>89790</v>
+        <v>82680</v>
       </c>
       <c r="Q5" t="n">
-        <v>65212.01</v>
+        <v>675785.74</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>44160</v>
       </c>
       <c r="H6" t="n">
-        <v>4320</v>
+        <v>6000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>106320</v>
+        <v>147060</v>
       </c>
       <c r="M6" t="n">
-        <v>7770</v>
+        <v>33900</v>
       </c>
       <c r="N6" t="n">
-        <v>2760</v>
+        <v>7140</v>
       </c>
       <c r="O6" t="n">
-        <v>40770</v>
+        <v>56250</v>
       </c>
       <c r="P6" t="n">
-        <v>90840</v>
+        <v>91590</v>
       </c>
       <c r="Q6" t="n">
-        <v>26825.74</v>
+        <v>277992.53</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>17220</v>
       </c>
       <c r="H7" t="n">
-        <v>390</v>
+        <v>750</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -731,22 +731,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50100</v>
+        <v>85110</v>
       </c>
       <c r="M7" t="n">
-        <v>4410</v>
+        <v>25770</v>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="O7" t="n">
-        <v>11340</v>
+        <v>23730</v>
       </c>
       <c r="P7" t="n">
-        <v>92910</v>
+        <v>101100</v>
       </c>
       <c r="Q7" t="n">
-        <v>16256.88</v>
+        <v>168468.51</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>10170</v>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>55500</v>
+      </c>
+      <c r="M8" t="n">
         <v>18960</v>
       </c>
-      <c r="M8" t="n">
-        <v>1380</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1530</v>
+        <v>6270</v>
       </c>
       <c r="P8" t="n">
-        <v>97290</v>
+        <v>147750</v>
       </c>
       <c r="Q8" t="n">
-        <v>8973.98</v>
+        <v>92996.48</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>2700</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>7380</v>
+        <v>32970</v>
       </c>
       <c r="M9" t="n">
-        <v>450</v>
+        <v>11250</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="P9" t="n">
-        <v>58650</v>
+        <v>104760</v>
       </c>
       <c r="Q9" t="n">
-        <v>4662.09</v>
+        <v>48312.79</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>1020</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4260</v>
+        <v>33300</v>
       </c>
       <c r="M10" t="n">
-        <v>330</v>
+        <v>4590</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -902,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>39060</v>
+        <v>65640</v>
       </c>
       <c r="Q10" t="n">
-        <v>2401.52</v>
+        <v>24886.72</v>
       </c>
     </row>
     <row r="11">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2010</v>
+        <v>11730</v>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>3060</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>27780</v>
+        <v>47610</v>
       </c>
       <c r="Q11" t="n">
-        <v>1422.79</v>
+        <v>14744.22</v>
       </c>
     </row>
     <row r="12">
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>420</v>
+        <v>4260</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3870</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>17790</v>
+        <v>41100</v>
       </c>
       <c r="Q12" t="n">
-        <v>1066.9</v>
+        <v>11056.14</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>180</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>240</v>
+        <v>2760</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7890</v>
+        <v>17130</v>
       </c>
       <c r="Q13" t="n">
-        <v>1064.33</v>
+        <v>11029.54</v>
       </c>
     </row>
     <row r="14">
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>570</v>
+        <v>2190</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1020</v>
+        <v>2160</v>
       </c>
       <c r="Q14" t="n">
-        <v>1088.21</v>
+        <v>11277.03</v>
       </c>
     </row>
     <row r="15">
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>462.25</v>
+        <v>4790.22</v>
       </c>
     </row>
     <row r="16">
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>173.98</v>
+        <v>1802.98</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>36.83</v>
+        <v>381.64</v>
       </c>
     </row>
     <row r="18">
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.68</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="19">
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1852,7 @@
         <v>28590</v>
       </c>
       <c r="H4" t="n">
-        <v>2580</v>
+        <v>4500</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>72960</v>
+        <v>92820</v>
       </c>
       <c r="M4" t="n">
-        <v>8100</v>
+        <v>10140</v>
       </c>
       <c r="N4" t="n">
-        <v>60</v>
+        <v>780</v>
       </c>
       <c r="O4" t="n">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1701.54</v>
+        <v>192841.2</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>16020</v>
       </c>
       <c r="H5" t="n">
-        <v>2130</v>
+        <v>1920</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1917,10 +1917,10 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>44310</v>
+        <v>53910</v>
       </c>
       <c r="M5" t="n">
-        <v>8670</v>
+        <v>13380</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1265.33</v>
+        <v>143403.84</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>9930</v>
       </c>
       <c r="H6" t="n">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>22920</v>
+        <v>30390</v>
       </c>
       <c r="M6" t="n">
-        <v>3210</v>
+        <v>8340</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1336.28</v>
+        <v>151445.52</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>3630</v>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9720</v>
+        <v>16740</v>
       </c>
       <c r="M7" t="n">
-        <v>1980</v>
+        <v>4080</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1077.97</v>
+        <v>122170.5</v>
       </c>
     </row>
     <row r="8">
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3000</v>
+        <v>6510</v>
       </c>
       <c r="M8" t="n">
-        <v>600</v>
+        <v>2190</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>676.1900000000001</v>
+        <v>76634.64</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>870</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>960</v>
+        <v>2550</v>
       </c>
       <c r="M9" t="n">
-        <v>150</v>
+        <v>1050</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>291.52</v>
+        <v>33038.82</v>
       </c>
     </row>
     <row r="10">
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>660</v>
+        <v>1080</v>
       </c>
       <c r="M10" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>131.08</v>
+        <v>14856.3</v>
       </c>
     </row>
     <row r="11">
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1170</v>
+        <v>2370</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1770</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>88.13</v>
+        <v>9987.84</v>
       </c>
     </row>
     <row r="12">
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>1290</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.95</v>
+        <v>8268.120000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,11 +2341,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.64</v>
+        <v>9706.32</v>
       </c>
     </row>
     <row r="14">
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.84999999999999</v>
+        <v>10863</v>
       </c>
     </row>
     <row r="15">
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.83</v>
+        <v>4287.06</v>
       </c>
     </row>
     <row r="16">
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.97</v>
+        <v>3283.38</v>
       </c>
     </row>
     <row r="17">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>766.8</v>
+        <v>691.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -3209,10 +3209,10 @@
         <v>2.32</v>
       </c>
       <c r="L5" t="n">
-        <v>9305.1</v>
+        <v>11321.1</v>
       </c>
       <c r="M5" t="n">
-        <v>173.4</v>
+        <v>267.6</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.27</v>
+        <v>7170.19</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>496.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1881</v>
+        <v>2223</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>8480.4</v>
+        <v>11244.3</v>
       </c>
       <c r="M6" t="n">
-        <v>256.8</v>
+        <v>667.2</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1002.21</v>
+        <v>113584.14</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>544.5</v>
       </c>
       <c r="H7" t="n">
-        <v>65.7</v>
+        <v>262.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5832</v>
+        <v>10044</v>
       </c>
       <c r="M7" t="n">
-        <v>693</v>
+        <v>1428</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>862.38</v>
+        <v>97736.39999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2130</v>
+        <v>4622.1</v>
       </c>
       <c r="M8" t="n">
-        <v>330</v>
+        <v>1204.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>642.38</v>
+        <v>72802.91</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>739.5</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>777.6</v>
+        <v>2065.5</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>735</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>282.77</v>
+        <v>32047.66</v>
       </c>
     </row>
     <row r="10">
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>587.4</v>
+        <v>961.2</v>
       </c>
       <c r="M10" t="n">
-        <v>51</v>
+        <v>637.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>131.08</v>
+        <v>14856.3</v>
       </c>
     </row>
     <row r="11">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1170</v>
+        <v>2370</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>88.13</v>
+        <v>9987.84</v>
       </c>
     </row>
     <row r="12">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>1290</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.95</v>
+        <v>8268.120000000001</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,11 +3633,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.64</v>
+        <v>9706.32</v>
       </c>
     </row>
     <row r="14">
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.84999999999999</v>
+        <v>10863</v>
       </c>
     </row>
     <row r="15">
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.83</v>
+        <v>4287.06</v>
       </c>
     </row>
     <row r="16">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.97</v>
+        <v>3283.38</v>
       </c>
     </row>
     <row r="17">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4370760</v>
+        <v>3939840</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -4501,10 +4501,10 @@
         <v>112504.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1674918</v>
+        <v>2037798</v>
       </c>
       <c r="M5" t="n">
-        <v>60690</v>
+        <v>93660</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>37959.84</v>
+        <v>4302115.2</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>26811</v>
       </c>
       <c r="H6" t="n">
-        <v>10721700</v>
+        <v>12671100</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1526472</v>
+        <v>2023974</v>
       </c>
       <c r="M6" t="n">
-        <v>89880</v>
+        <v>233520</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5100</v>
+        <v>10200</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>601327.8</v>
+        <v>68150484</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>29403</v>
       </c>
       <c r="H7" t="n">
-        <v>374490</v>
+        <v>1497960</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1049760</v>
+        <v>1807920</v>
       </c>
       <c r="M7" t="n">
-        <v>242550</v>
+        <v>499800</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>517428</v>
+        <v>58641840</v>
       </c>
     </row>
     <row r="8">
@@ -4660,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>383400</v>
+        <v>831978</v>
       </c>
       <c r="M8" t="n">
-        <v>115500</v>
+        <v>421575</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385427.16</v>
+        <v>43681744.8</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>39933</v>
       </c>
       <c r="H9" t="n">
-        <v>342000</v>
+        <v>1026000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>139968</v>
+        <v>371790</v>
       </c>
       <c r="M9" t="n">
-        <v>36750</v>
+        <v>257250</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>169664.06</v>
+        <v>19228593.24</v>
       </c>
     </row>
     <row r="10">
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>105732</v>
+        <v>173016</v>
       </c>
       <c r="M10" t="n">
-        <v>17850</v>
+        <v>223125</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>78651</v>
+        <v>8913780</v>
       </c>
     </row>
     <row r="11">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210600</v>
+        <v>426600</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>557550</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>52876.8</v>
+        <v>5992704</v>
       </c>
     </row>
     <row r="12">
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>43200</v>
+        <v>232200</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>219450</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>43772.4</v>
+        <v>4960872</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16200</v>
+        <v>75600</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>51386.4</v>
+        <v>5823792</v>
       </c>
     </row>
     <row r="14">
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57510</v>
+        <v>6517800</v>
       </c>
     </row>
     <row r="15">
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22696.2</v>
+        <v>2572236</v>
       </c>
     </row>
     <row r="16">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17382.6</v>
+        <v>1970028</v>
       </c>
     </row>
     <row r="17">
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>259.2</v>
+        <v>29376</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.8</v>
+        <v>34884</v>
       </c>
     </row>
     <row r="19">
@@ -5728,7 +5728,7 @@
         <v>13740</v>
       </c>
       <c r="H4" t="n">
-        <v>930</v>
+        <v>2040</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>46890</v>
+        <v>67080</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2220</v>
+        <v>2730</v>
       </c>
       <c r="O4" t="n">
-        <v>13440</v>
+        <v>17190</v>
       </c>
       <c r="P4" t="n">
-        <v>8700</v>
+        <v>11010</v>
       </c>
       <c r="Q4" t="n">
-        <v>8063.54</v>
+        <v>42439.68</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>1980</v>
       </c>
       <c r="H5" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>7710</v>
+        <v>12390</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>480</v>
+        <v>960</v>
       </c>
       <c r="O5" t="n">
-        <v>1590</v>
+        <v>3150</v>
       </c>
       <c r="P5" t="n">
-        <v>6630</v>
+        <v>11460</v>
       </c>
       <c r="Q5" t="n">
-        <v>956.03</v>
+        <v>5031.72</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>450</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1230</v>
+        <v>3270</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -5855,13 +5855,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P6" t="n">
-        <v>6030</v>
+        <v>11880</v>
       </c>
       <c r="Q6" t="n">
-        <v>75.72</v>
+        <v>398.52</v>
       </c>
     </row>
     <row r="7">
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>270</v>
+        <v>1110</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3930</v>
+        <v>9990</v>
       </c>
       <c r="Q7" t="n">
-        <v>34.88</v>
+        <v>183.6</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>720</v>
+        <v>2040</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.67</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="9">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>86.40000000000001</v>
+        <v>108</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>0.33</v>
       </c>
       <c r="L5" t="n">
-        <v>1619.1</v>
+        <v>2601.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="O5" t="n">
-        <v>79.5</v>
+        <v>157.5</v>
       </c>
       <c r="P5" t="n">
-        <v>132.6</v>
+        <v>229.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>47.8</v>
+        <v>251.59</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>22.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>455.1</v>
+        <v>1209.9</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="P6" t="n">
-        <v>904.5</v>
+        <v>1782</v>
       </c>
       <c r="Q6" t="n">
-        <v>56.79</v>
+        <v>298.89</v>
       </c>
     </row>
     <row r="7">
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>162</v>
+        <v>666</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>982.5</v>
+        <v>2497.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.91</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>447.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>273.6</v>
+        <v>775.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.53</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="9">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>492480</v>
+        <v>615600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>16072.04</v>
       </c>
       <c r="L5" t="n">
-        <v>291438</v>
+        <v>468342</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>816</v>
+        <v>1632</v>
       </c>
       <c r="O5" t="n">
-        <v>13515</v>
+        <v>26775</v>
       </c>
       <c r="P5" t="n">
-        <v>8619</v>
+        <v>14898</v>
       </c>
       <c r="Q5" t="n">
-        <v>28680.8</v>
+        <v>150951.6</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>1215</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>389880</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>81918</v>
+        <v>217782</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3825</v>
       </c>
       <c r="P6" t="n">
-        <v>58792.5</v>
+        <v>115830</v>
       </c>
       <c r="Q6" t="n">
-        <v>34073.46</v>
+        <v>179334</v>
       </c>
     </row>
     <row r="7">
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>29160</v>
+        <v>119880</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>63862.5</v>
+        <v>162337.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>16744.32</v>
+        <v>88128</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>80514</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>17784</v>
+        <v>50388</v>
       </c>
       <c r="Q8" t="n">
-        <v>1520.53</v>
+        <v>8002.8</v>
       </c>
     </row>
     <row r="9">
@@ -9604,7 +9604,7 @@
         <v>13770</v>
       </c>
       <c r="H4" t="n">
-        <v>2520</v>
+        <v>2670</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>14610</v>
+        <v>20850</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>10680</v>
+        <v>15300</v>
       </c>
       <c r="O4" t="n">
-        <v>30660</v>
+        <v>29100</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6738.21</v>
+        <v>36563.94</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>2730</v>
       </c>
       <c r="H5" t="n">
-        <v>810</v>
+        <v>1080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4320</v>
+        <v>6030</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4230</v>
+        <v>3090</v>
       </c>
       <c r="O5" t="n">
-        <v>31830</v>
+        <v>33450</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>982.3200000000001</v>
+        <v>5330.43</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>990</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>300</v>
+        <v>1980</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1560</v>
+        <v>3750</v>
       </c>
       <c r="O6" t="n">
-        <v>10110</v>
+        <v>14760</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>177.28</v>
+        <v>962.01</v>
       </c>
     </row>
     <row r="7">
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="O7" t="n">
-        <v>1140</v>
+        <v>2370</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.79</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>690</v>
+        <v>930</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.18</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="9">
@@ -9890,7 +9890,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>291.6</v>
+        <v>388.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>907.2</v>
+        <v>1266.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>42.3</v>
+        <v>30.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1591.5</v>
+        <v>1672.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>49.12</v>
+        <v>266.52</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>49.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>205.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>111</v>
+        <v>732.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>78</v>
+        <v>187.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2527.5</v>
+        <v>3690</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>132.96</v>
+        <v>721.51</v>
       </c>
     </row>
     <row r="7">
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.4</v>
+        <v>44.1</v>
       </c>
       <c r="O7" t="n">
-        <v>399</v>
+        <v>829.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.63</v>
+        <v>68.54000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>310.5</v>
+        <v>418.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.97</v>
+        <v>21.55</v>
       </c>
     </row>
     <row r="9">
@@ -11182,7 +11182,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>49.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1662120</v>
+        <v>2216160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>163296</v>
+        <v>227934</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7191</v>
+        <v>5253</v>
       </c>
       <c r="O5" t="n">
-        <v>270555</v>
+        <v>284325</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29469.66</v>
+        <v>159912.9</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>2673</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1169640</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>19980</v>
+        <v>131868</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>13260</v>
+        <v>31875</v>
       </c>
       <c r="O6" t="n">
-        <v>429675</v>
+        <v>627300</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>79778.12</v>
+        <v>432904.5</v>
       </c>
     </row>
     <row r="7">
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3240</v>
+        <v>16200</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1428</v>
+        <v>7497</v>
       </c>
       <c r="O7" t="n">
-        <v>67830</v>
+        <v>141015</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7579.01</v>
+        <v>41126.4</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>52785</v>
+        <v>71145</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2382.37</v>
+        <v>12927.6</v>
       </c>
     </row>
     <row r="9">
@@ -12474,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2805</v>
+        <v>8415</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -13480,7 +13480,7 @@
         <v>89910</v>
       </c>
       <c r="H4" t="n">
-        <v>15150</v>
+        <v>17100</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -13492,19 +13492,19 @@
         <v>96</v>
       </c>
       <c r="L4" t="n">
-        <v>215520</v>
+        <v>228060</v>
       </c>
       <c r="M4" t="n">
-        <v>12150</v>
+        <v>9480</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>63990</v>
+        <v>76440</v>
       </c>
       <c r="P4" t="n">
-        <v>44340</v>
+        <v>23430</v>
       </c>
       <c r="Q4" t="n">
         <v>47583.45</v>
@@ -13533,7 +13533,7 @@
         <v>28890</v>
       </c>
       <c r="H5" t="n">
-        <v>3600</v>
+        <v>4320</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -13545,19 +13545,19 @@
         <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>91680</v>
+        <v>97740</v>
       </c>
       <c r="M5" t="n">
-        <v>4710</v>
+        <v>12900</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>21390</v>
+        <v>30840</v>
       </c>
       <c r="P5" t="n">
-        <v>43890</v>
+        <v>41760</v>
       </c>
       <c r="Q5" t="n">
         <v>21575.85</v>
@@ -13586,7 +13586,7 @@
         <v>6480</v>
       </c>
       <c r="H6" t="n">
-        <v>480</v>
+        <v>840</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -13598,19 +13598,19 @@
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>29070</v>
+        <v>35220</v>
       </c>
       <c r="M6" t="n">
-        <v>2580</v>
+        <v>13110</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>11040</v>
+        <v>11190</v>
       </c>
       <c r="P6" t="n">
-        <v>40650</v>
+        <v>43650</v>
       </c>
       <c r="Q6" t="n">
         <v>3530.8</v>
@@ -13639,7 +13639,7 @@
         <v>780</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -13651,19 +13651,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>11430</v>
+        <v>24210</v>
       </c>
       <c r="M7" t="n">
-        <v>840</v>
+        <v>12450</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7110</v>
+        <v>9360</v>
       </c>
       <c r="P7" t="n">
-        <v>42360</v>
+        <v>50100</v>
       </c>
       <c r="Q7" t="n">
         <v>1611.73</v>
@@ -13704,19 +13704,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4320</v>
+        <v>24960</v>
       </c>
       <c r="M8" t="n">
-        <v>330</v>
+        <v>9450</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>420</v>
+        <v>1350</v>
       </c>
       <c r="P8" t="n">
-        <v>36750</v>
+        <v>57330</v>
       </c>
       <c r="Q8" t="n">
         <v>173.76</v>
@@ -13757,19 +13757,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3120</v>
+        <v>21510</v>
       </c>
       <c r="M9" t="n">
-        <v>180</v>
+        <v>5970</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>31680</v>
+        <v>57090</v>
       </c>
       <c r="Q9" t="n">
         <v>123.88</v>
@@ -13798,7 +13798,7 @@
         <v>270</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13810,10 +13810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2190</v>
+        <v>26280</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>2280</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>19590</v>
+        <v>36540</v>
       </c>
       <c r="Q10" t="n">
         <v>62.05</v>
@@ -13863,10 +13863,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>480</v>
+        <v>8400</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15750</v>
+        <v>26550</v>
       </c>
       <c r="Q11" t="n">
         <v>15.85</v>
@@ -13916,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>2610</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7440</v>
+        <v>21210</v>
       </c>
       <c r="Q12" t="n">
         <v>7.48</v>
@@ -13969,7 +13969,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3360</v>
+        <v>8070</v>
       </c>
       <c r="Q13" t="n">
         <v>3.79</v>
@@ -14022,7 +14022,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>690</v>
+        <v>1470</v>
       </c>
       <c r="Q14" t="n">
         <v>0.89</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4417.2</v>
+        <v>5637.6</v>
       </c>
       <c r="I5" t="n">
         <v>1.32</v>
@@ -14837,22 +14837,22 @@
         <v>14.23</v>
       </c>
       <c r="L5" t="n">
-        <v>71145.89999999999</v>
+        <v>88521.3</v>
       </c>
       <c r="M5" t="n">
-        <v>406.8</v>
+        <v>988.8</v>
       </c>
       <c r="N5" t="n">
-        <v>125.7</v>
+        <v>157.8</v>
       </c>
       <c r="O5" t="n">
-        <v>5311.5</v>
+        <v>6829.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1795.8</v>
+        <v>1653.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>3260.6</v>
+        <v>33789.29</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>2208</v>
       </c>
       <c r="H6" t="n">
-        <v>2462.4</v>
+        <v>3420</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -14890,22 +14890,22 @@
         <v>4.06</v>
       </c>
       <c r="L6" t="n">
-        <v>39338.4</v>
+        <v>54412.2</v>
       </c>
       <c r="M6" t="n">
-        <v>621.6</v>
+        <v>2712</v>
       </c>
       <c r="N6" t="n">
-        <v>138</v>
+        <v>357</v>
       </c>
       <c r="O6" t="n">
-        <v>10192.5</v>
+        <v>14062.5</v>
       </c>
       <c r="P6" t="n">
-        <v>13626</v>
+        <v>13738.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>20119.3</v>
+        <v>208494.4</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>2583</v>
       </c>
       <c r="H7" t="n">
-        <v>284.7</v>
+        <v>547.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -14943,22 +14943,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>30060</v>
+        <v>51066</v>
       </c>
       <c r="M7" t="n">
-        <v>1543.5</v>
+        <v>9019.5</v>
       </c>
       <c r="N7" t="n">
-        <v>8.4</v>
+        <v>44.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3969</v>
+        <v>8305.5</v>
       </c>
       <c r="P7" t="n">
-        <v>23227.5</v>
+        <v>25275</v>
       </c>
       <c r="Q7" t="n">
-        <v>13005.51</v>
+        <v>134774.81</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>6610.5</v>
       </c>
       <c r="H8" t="n">
-        <v>76.5</v>
+        <v>255</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -14996,22 +14996,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>13461.6</v>
+        <v>39405</v>
       </c>
       <c r="M8" t="n">
-        <v>759</v>
+        <v>10428</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>688.5</v>
+        <v>2821.5</v>
       </c>
       <c r="P8" t="n">
-        <v>36970.2</v>
+        <v>56145</v>
       </c>
       <c r="Q8" t="n">
-        <v>8525.280000000001</v>
+        <v>88346.64999999999</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>2295</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>5977.8</v>
+        <v>26705.7</v>
       </c>
       <c r="M9" t="n">
-        <v>315</v>
+        <v>7875</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>132</v>
       </c>
       <c r="P9" t="n">
-        <v>29325</v>
+        <v>52380</v>
       </c>
       <c r="Q9" t="n">
-        <v>4522.23</v>
+        <v>46863.4</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>1020</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,10 +15102,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3791.4</v>
+        <v>29637</v>
       </c>
       <c r="M10" t="n">
-        <v>280.5</v>
+        <v>3901.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -15114,10 +15114,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>33201</v>
+        <v>55794</v>
       </c>
       <c r="Q10" t="n">
-        <v>2401.52</v>
+        <v>24886.72</v>
       </c>
     </row>
     <row r="11">
@@ -15155,10 +15155,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2010</v>
+        <v>11730</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>2754</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -15167,10 +15167,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>25002</v>
+        <v>42849</v>
       </c>
       <c r="Q11" t="n">
-        <v>1422.79</v>
+        <v>14744.22</v>
       </c>
     </row>
     <row r="12">
@@ -15208,10 +15208,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>420</v>
+        <v>4260</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3676.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -15220,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>17790</v>
+        <v>41100</v>
       </c>
       <c r="Q12" t="n">
-        <v>1066.9</v>
+        <v>11056.14</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>180</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>240</v>
+        <v>2760</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -15273,10 +15273,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7890</v>
+        <v>17130</v>
       </c>
       <c r="Q13" t="n">
-        <v>1064.33</v>
+        <v>11029.54</v>
       </c>
     </row>
     <row r="14">
@@ -15314,10 +15314,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>570</v>
+        <v>2190</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -15326,10 +15326,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1020</v>
+        <v>2160</v>
       </c>
       <c r="Q14" t="n">
-        <v>1088.21</v>
+        <v>11277.03</v>
       </c>
     </row>
     <row r="15">
@@ -15367,10 +15367,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -15382,7 +15382,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>462.25</v>
+        <v>4790.22</v>
       </c>
     </row>
     <row r="16">
@@ -15420,7 +15420,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -15435,7 +15435,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>173.98</v>
+        <v>1802.98</v>
       </c>
     </row>
     <row r="17">
@@ -15473,7 +15473,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -15488,7 +15488,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>36.83</v>
+        <v>381.64</v>
       </c>
     </row>
     <row r="18">
@@ -15526,7 +15526,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.68</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="19">
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1296</v>
+        <v>1555.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -16129,19 +16129,19 @@
         <v>5.63</v>
       </c>
       <c r="L5" t="n">
-        <v>19252.8</v>
+        <v>20525.4</v>
       </c>
       <c r="M5" t="n">
-        <v>94.2</v>
+        <v>258</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1069.5</v>
+        <v>1542</v>
       </c>
       <c r="P5" t="n">
-        <v>877.8</v>
+        <v>835.2</v>
       </c>
       <c r="Q5" t="n">
         <v>1078.79</v>
@@ -16170,7 +16170,7 @@
         <v>324</v>
       </c>
       <c r="H6" t="n">
-        <v>273.6</v>
+        <v>478.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -16182,19 +16182,19 @@
         <v>2.54</v>
       </c>
       <c r="L6" t="n">
-        <v>10755.9</v>
+        <v>13031.4</v>
       </c>
       <c r="M6" t="n">
-        <v>206.4</v>
+        <v>1048.8</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2760</v>
+        <v>2797.5</v>
       </c>
       <c r="P6" t="n">
-        <v>6097.5</v>
+        <v>6547.5</v>
       </c>
       <c r="Q6" t="n">
         <v>2648.1</v>
@@ -16223,7 +16223,7 @@
         <v>117</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -16235,19 +16235,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6858</v>
+        <v>14526</v>
       </c>
       <c r="M7" t="n">
-        <v>294</v>
+        <v>4357.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2488.5</v>
+        <v>3276</v>
       </c>
       <c r="P7" t="n">
-        <v>10590</v>
+        <v>12525</v>
       </c>
       <c r="Q7" t="n">
         <v>1289.38</v>
@@ -16288,19 +16288,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3067.2</v>
+        <v>17721.6</v>
       </c>
       <c r="M8" t="n">
-        <v>181.5</v>
+        <v>5197.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>189</v>
+        <v>607.5</v>
       </c>
       <c r="P8" t="n">
-        <v>13965</v>
+        <v>21785.4</v>
       </c>
       <c r="Q8" t="n">
         <v>165.07</v>
@@ -16341,19 +16341,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2527.2</v>
+        <v>17423.1</v>
       </c>
       <c r="M9" t="n">
-        <v>126</v>
+        <v>4179</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="P9" t="n">
-        <v>15840</v>
+        <v>28545</v>
       </c>
       <c r="Q9" t="n">
         <v>120.16</v>
@@ -16382,7 +16382,7 @@
         <v>270</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16394,10 +16394,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1949.1</v>
+        <v>23389.2</v>
       </c>
       <c r="M10" t="n">
-        <v>25.5</v>
+        <v>1938</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>16651.5</v>
+        <v>31059</v>
       </c>
       <c r="Q10" t="n">
         <v>62.05</v>
@@ -16447,10 +16447,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>480</v>
+        <v>8400</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>14175</v>
+        <v>23895</v>
       </c>
       <c r="Q11" t="n">
         <v>15.85</v>
@@ -16500,10 +16500,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>2610</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7440</v>
+        <v>21210</v>
       </c>
       <c r="Q12" t="n">
         <v>7.48</v>
@@ -16553,7 +16553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3360</v>
+        <v>8070</v>
       </c>
       <c r="Q13" t="n">
         <v>3.79</v>
@@ -16606,7 +16606,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>690</v>
+        <v>1470</v>
       </c>
       <c r="Q14" t="n">
         <v>0.89</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7387200</v>
+        <v>8864640</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -17421,19 +17421,19 @@
         <v>273224.61</v>
       </c>
       <c r="L5" t="n">
-        <v>3465504</v>
+        <v>3694572</v>
       </c>
       <c r="M5" t="n">
-        <v>32970</v>
+        <v>90300</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>181815</v>
+        <v>262140</v>
       </c>
       <c r="P5" t="n">
-        <v>57057</v>
+        <v>54288</v>
       </c>
       <c r="Q5" t="n">
         <v>647275.54</v>
@@ -17462,7 +17462,7 @@
         <v>17496</v>
       </c>
       <c r="H6" t="n">
-        <v>1559520</v>
+        <v>2729160</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17474,19 +17474,19 @@
         <v>123089.46</v>
       </c>
       <c r="L6" t="n">
-        <v>1936062</v>
+        <v>2345652</v>
       </c>
       <c r="M6" t="n">
-        <v>72240</v>
+        <v>367080</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>469200</v>
+        <v>475575</v>
       </c>
       <c r="P6" t="n">
-        <v>396337.5</v>
+        <v>425587.5</v>
       </c>
       <c r="Q6" t="n">
         <v>1588860.36</v>
@@ -17515,7 +17515,7 @@
         <v>6318</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>249660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -17527,19 +17527,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1234440</v>
+        <v>2614680</v>
       </c>
       <c r="M7" t="n">
-        <v>102900</v>
+        <v>1525125</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>423045</v>
+        <v>556920</v>
       </c>
       <c r="P7" t="n">
-        <v>688350</v>
+        <v>814125</v>
       </c>
       <c r="Q7" t="n">
         <v>773629.0600000001</v>
@@ -17580,19 +17580,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>552096</v>
+        <v>3189888</v>
       </c>
       <c r="M8" t="n">
-        <v>63525</v>
+        <v>1819125</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>32130</v>
+        <v>103275</v>
       </c>
       <c r="P8" t="n">
-        <v>907725</v>
+        <v>1416051</v>
       </c>
       <c r="Q8" t="n">
         <v>99043.88</v>
@@ -17633,19 +17633,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>454896</v>
+        <v>3136158</v>
       </c>
       <c r="M9" t="n">
-        <v>44100</v>
+        <v>1462650</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2805</v>
       </c>
       <c r="P9" t="n">
-        <v>1029600</v>
+        <v>1855425</v>
       </c>
       <c r="Q9" t="n">
         <v>72095.83</v>
@@ -17674,7 +17674,7 @@
         <v>14580</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -17686,10 +17686,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>350838</v>
+        <v>4210056</v>
       </c>
       <c r="M10" t="n">
-        <v>8925</v>
+        <v>678300</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -17698,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1082347.5</v>
+        <v>2018835</v>
       </c>
       <c r="Q10" t="n">
         <v>37229.76</v>
@@ -17739,10 +17739,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>86400</v>
+        <v>1512000</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>75600</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>921375</v>
+        <v>1553175</v>
       </c>
       <c r="Q11" t="n">
         <v>9508.32</v>
@@ -17792,10 +17792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16200</v>
+        <v>469800</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>19950</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>483600</v>
+        <v>1378650</v>
       </c>
       <c r="Q12" t="n">
         <v>4486.32</v>
@@ -17845,7 +17845,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>378000</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>218400</v>
+        <v>524550</v>
       </c>
       <c r="Q13" t="n">
         <v>2276.64</v>
@@ -17898,7 +17898,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5400</v>
+        <v>140400</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>44850</v>
+        <v>95550</v>
       </c>
       <c r="Q14" t="n">
         <v>535.6799999999999</v>
@@ -18648,7 +18648,7 @@
         <v>28980</v>
       </c>
       <c r="H4" t="n">
-        <v>2670</v>
+        <v>3420</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -18660,22 +18660,22 @@
         <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>112770</v>
+        <v>145890</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2790</v>
+        <v>3690</v>
       </c>
       <c r="O4" t="n">
-        <v>39810</v>
+        <v>49710</v>
       </c>
       <c r="P4" t="n">
-        <v>3630</v>
+        <v>4320</v>
       </c>
       <c r="Q4" t="n">
-        <v>9110.1</v>
+        <v>104386.59</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>3900</v>
       </c>
       <c r="H5" t="n">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>24090</v>
+        <v>34260</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="O5" t="n">
-        <v>10770</v>
+        <v>16020</v>
       </c>
       <c r="P5" t="n">
-        <v>1470</v>
+        <v>5100</v>
       </c>
       <c r="Q5" t="n">
-        <v>1157.85</v>
+        <v>13266.99</v>
       </c>
     </row>
     <row r="6">
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4920</v>
+        <v>7680</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>1590</v>
+        <v>3270</v>
       </c>
       <c r="P6" t="n">
-        <v>540</v>
+        <v>2220</v>
       </c>
       <c r="Q6" t="n">
-        <v>128.3</v>
+        <v>1470.15</v>
       </c>
     </row>
     <row r="7">
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -18831,10 +18831,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>420</v>
+        <v>1860</v>
       </c>
       <c r="Q7" t="n">
-        <v>39.05</v>
+        <v>447.48</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.35</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>129.6</v>
+        <v>216</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5058.9</v>
+        <v>7194.6</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
-        <v>538.5</v>
+        <v>801</v>
       </c>
       <c r="P5" t="n">
-        <v>29.4</v>
+        <v>102</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.89</v>
+        <v>663.35</v>
       </c>
     </row>
     <row r="6">
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1820.4</v>
+        <v>2841.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>397.5</v>
+        <v>817.5</v>
       </c>
       <c r="P6" t="n">
-        <v>81</v>
+        <v>333</v>
       </c>
       <c r="Q6" t="n">
-        <v>96.23</v>
+        <v>1102.61</v>
       </c>
     </row>
     <row r="7">
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -20123,10 +20123,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>105</v>
+        <v>465</v>
       </c>
       <c r="Q7" t="n">
-        <v>31.24</v>
+        <v>357.98</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>42.6</v>
+        <v>106.5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>11.4</v>
+        <v>136.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.33</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>145.8</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>80.09999999999999</v>
+        <v>160.2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>738720</v>
+        <v>1231200</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>910602</v>
+        <v>1295028</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>816</v>
+        <v>1071</v>
       </c>
       <c r="O5" t="n">
-        <v>91545</v>
+        <v>136170</v>
       </c>
       <c r="P5" t="n">
-        <v>1911</v>
+        <v>6630</v>
       </c>
       <c r="Q5" t="n">
-        <v>34735.39</v>
+        <v>398009.7</v>
       </c>
     </row>
     <row r="6">
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>327672</v>
+        <v>511488</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>67575</v>
+        <v>138975</v>
       </c>
       <c r="P6" t="n">
-        <v>5265</v>
+        <v>21645</v>
       </c>
       <c r="Q6" t="n">
-        <v>57736.8</v>
+        <v>661567.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>19440</v>
+        <v>35640</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -21415,10 +21415,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6825</v>
+        <v>30225</v>
       </c>
       <c r="Q7" t="n">
-        <v>18745.34</v>
+        <v>214790.4</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7668</v>
+        <v>19170</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>741</v>
+        <v>8892</v>
       </c>
       <c r="Q8" t="n">
-        <v>196.99</v>
+        <v>2257.2</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26244</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>14418</v>
+        <v>28836</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>25178040</v>
+        <v>32134320</v>
       </c>
       <c r="I5" t="n">
         <v>257152.58</v>
@@ -22589,22 +22589,22 @@
         <v>691097.55</v>
       </c>
       <c r="L5" t="n">
-        <v>12806262</v>
+        <v>15933834</v>
       </c>
       <c r="M5" t="n">
-        <v>142380</v>
+        <v>346080</v>
       </c>
       <c r="N5" t="n">
-        <v>21369</v>
+        <v>26826</v>
       </c>
       <c r="O5" t="n">
-        <v>902955</v>
+        <v>1161015</v>
       </c>
       <c r="P5" t="n">
-        <v>116727</v>
+        <v>107484</v>
       </c>
       <c r="Q5" t="n">
-        <v>1956360.28</v>
+        <v>20273572.22</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>119232</v>
       </c>
       <c r="H6" t="n">
-        <v>14035680</v>
+        <v>19494000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22642,22 +22642,22 @@
         <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>7080912</v>
+        <v>9794196</v>
       </c>
       <c r="M6" t="n">
-        <v>217560</v>
+        <v>949200</v>
       </c>
       <c r="N6" t="n">
-        <v>23460</v>
+        <v>60690</v>
       </c>
       <c r="O6" t="n">
-        <v>1732725</v>
+        <v>2390625</v>
       </c>
       <c r="P6" t="n">
-        <v>885690</v>
+        <v>893002.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>12071582.28</v>
+        <v>125096638.95</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>139482</v>
       </c>
       <c r="H7" t="n">
-        <v>1622790</v>
+        <v>3120750</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22695,22 +22695,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5410800</v>
+        <v>9191880</v>
       </c>
       <c r="M7" t="n">
-        <v>540225</v>
+        <v>3156825</v>
       </c>
       <c r="N7" t="n">
-        <v>1428</v>
+        <v>7497</v>
       </c>
       <c r="O7" t="n">
-        <v>674730</v>
+        <v>1411935</v>
       </c>
       <c r="P7" t="n">
-        <v>1509787.5</v>
+        <v>1642875</v>
       </c>
       <c r="Q7" t="n">
-        <v>7803304.13</v>
+        <v>80864885.52</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>356967</v>
       </c>
       <c r="H8" t="n">
-        <v>436050</v>
+        <v>1453500</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22748,22 +22748,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2423088</v>
+        <v>7092900</v>
       </c>
       <c r="M8" t="n">
-        <v>265650</v>
+        <v>3649800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>117045</v>
+        <v>479655</v>
       </c>
       <c r="P8" t="n">
-        <v>2403063</v>
+        <v>3649425</v>
       </c>
       <c r="Q8" t="n">
-        <v>5115168.14</v>
+        <v>53007992.46</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>123930</v>
       </c>
       <c r="H9" t="n">
-        <v>684000</v>
+        <v>2565000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>1076004</v>
+        <v>4807026</v>
       </c>
       <c r="M9" t="n">
-        <v>110250</v>
+        <v>2756250</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2805</v>
+        <v>22440</v>
       </c>
       <c r="P9" t="n">
-        <v>1906125</v>
+        <v>3404700</v>
       </c>
       <c r="Q9" t="n">
-        <v>2713336.38</v>
+        <v>28118042.32</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>55080</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,10 +22854,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>682452</v>
+        <v>5334660</v>
       </c>
       <c r="M10" t="n">
-        <v>98175</v>
+        <v>1365525</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -22866,10 +22866,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2158065</v>
+        <v>3626610</v>
       </c>
       <c r="Q10" t="n">
-        <v>1440912.24</v>
+        <v>14932034.1</v>
       </c>
     </row>
     <row r="11">
@@ -22907,10 +22907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>361800</v>
+        <v>2111400</v>
       </c>
       <c r="M11" t="n">
-        <v>9450</v>
+        <v>963900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -22919,10 +22919,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1625130</v>
+        <v>2785185</v>
       </c>
       <c r="Q11" t="n">
-        <v>853673.04</v>
+        <v>8846531.1</v>
       </c>
     </row>
     <row r="12">
@@ -22960,10 +22960,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>75600</v>
+        <v>766800</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1286775</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -22972,10 +22972,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1156350</v>
+        <v>2671500</v>
       </c>
       <c r="Q12" t="n">
-        <v>640137.6</v>
+        <v>6633684</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>9720</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,10 +23013,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>43200</v>
+        <v>496800</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>304500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>512850</v>
+        <v>1113450</v>
       </c>
       <c r="Q13" t="n">
-        <v>638597.52</v>
+        <v>6617724.3</v>
       </c>
     </row>
     <row r="14">
@@ -23066,10 +23066,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>102600</v>
+        <v>394200</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -23078,10 +23078,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>66300</v>
+        <v>140400</v>
       </c>
       <c r="Q14" t="n">
-        <v>652926.96</v>
+        <v>6766218.9</v>
       </c>
     </row>
     <row r="15">
@@ -23119,10 +23119,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>277348.32</v>
+        <v>2874133.8</v>
       </c>
     </row>
     <row r="16">
@@ -23172,7 +23172,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23187,7 +23187,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104390.64</v>
+        <v>1081790.1</v>
       </c>
     </row>
     <row r="17">
@@ -23225,7 +23225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -23240,7 +23240,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22096.8</v>
+        <v>228987</v>
       </c>
     </row>
     <row r="18">
@@ -23278,7 +23278,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -23293,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2209.68</v>
+        <v>22898.7</v>
       </c>
     </row>
     <row r="19">
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>133.92</v>
+        <v>1387.8</v>
       </c>
     </row>
     <row r="20">
@@ -23816,7 +23816,7 @@
         <v>76020</v>
       </c>
       <c r="H4" t="n">
-        <v>3750</v>
+        <v>5340</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>174570</v>
+        <v>235650</v>
       </c>
       <c r="M4" t="n">
-        <v>16590</v>
+        <v>48000</v>
       </c>
       <c r="N4" t="n">
-        <v>10410</v>
+        <v>15720</v>
       </c>
       <c r="O4" t="n">
-        <v>22710</v>
+        <v>46770</v>
       </c>
       <c r="P4" t="n">
-        <v>17310</v>
+        <v>10830</v>
       </c>
       <c r="Q4" t="n">
-        <v>28365.74</v>
+        <v>278095.5</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>35040</v>
       </c>
       <c r="H5" t="n">
-        <v>600</v>
+        <v>1110</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>68190</v>
+        <v>102840</v>
       </c>
       <c r="M5" t="n">
-        <v>3600</v>
+        <v>18390</v>
       </c>
       <c r="N5" t="n">
-        <v>2670</v>
+        <v>3480</v>
       </c>
       <c r="O5" t="n">
-        <v>4740</v>
+        <v>9000</v>
       </c>
       <c r="P5" t="n">
-        <v>19020</v>
+        <v>20580</v>
       </c>
       <c r="Q5" t="n">
-        <v>14230.74</v>
+        <v>139517.1</v>
       </c>
     </row>
     <row r="6">
@@ -23934,22 +23934,22 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>21120</v>
+        <v>35940</v>
       </c>
       <c r="M6" t="n">
-        <v>240</v>
+        <v>6570</v>
       </c>
       <c r="N6" t="n">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="O6" t="n">
-        <v>480</v>
+        <v>1620</v>
       </c>
       <c r="P6" t="n">
-        <v>19620</v>
+        <v>23250</v>
       </c>
       <c r="Q6" t="n">
-        <v>6314.28</v>
+        <v>61904.7</v>
       </c>
     </row>
     <row r="7">
@@ -23987,22 +23987,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8370</v>
+        <v>17910</v>
       </c>
       <c r="M7" t="n">
-        <v>60</v>
+        <v>3330</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>2910</v>
       </c>
       <c r="P7" t="n">
-        <v>23040</v>
+        <v>23280</v>
       </c>
       <c r="Q7" t="n">
-        <v>2484.48</v>
+        <v>24357.6</v>
       </c>
     </row>
     <row r="8">
@@ -24040,22 +24040,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2610</v>
+        <v>10500</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="P8" t="n">
-        <v>35100</v>
+        <v>53130</v>
       </c>
       <c r="Q8" t="n">
-        <v>1112.71</v>
+        <v>10908.9</v>
       </c>
     </row>
     <row r="9">
@@ -24093,10 +24093,10 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1080</v>
+        <v>3030</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -24105,10 +24105,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>8490</v>
+        <v>10110</v>
       </c>
       <c r="Q9" t="n">
-        <v>387.76</v>
+        <v>3801.6</v>
       </c>
     </row>
     <row r="10">
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>360</v>
+        <v>810</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -24158,10 +24158,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>11130</v>
+        <v>13740</v>
       </c>
       <c r="Q10" t="n">
-        <v>189.48</v>
+        <v>1857.6</v>
       </c>
     </row>
     <row r="11">
@@ -24199,7 +24199,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -24211,10 +24211,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>6300</v>
+        <v>10830</v>
       </c>
       <c r="Q11" t="n">
-        <v>100.8</v>
+        <v>988.2</v>
       </c>
     </row>
     <row r="12">
@@ -24252,7 +24252,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -24264,10 +24264,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4080</v>
+        <v>6270</v>
       </c>
       <c r="Q12" t="n">
-        <v>58.38</v>
+        <v>572.4</v>
       </c>
     </row>
     <row r="13">
@@ -24305,7 +24305,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -24317,10 +24317,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2430</v>
+        <v>5520</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.52</v>
+        <v>338.4</v>
       </c>
     </row>
     <row r="14">
@@ -24373,7 +24373,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.5</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="15">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>216</v>
+        <v>399.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>2.32</v>
       </c>
       <c r="L5" t="n">
-        <v>14319.9</v>
+        <v>21596.4</v>
       </c>
       <c r="M5" t="n">
-        <v>72</v>
+        <v>367.8</v>
       </c>
       <c r="N5" t="n">
-        <v>26.7</v>
+        <v>34.8</v>
       </c>
       <c r="O5" t="n">
-        <v>237</v>
+        <v>450</v>
       </c>
       <c r="P5" t="n">
-        <v>380.4</v>
+        <v>411.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>711.54</v>
+        <v>6975.86</v>
       </c>
     </row>
     <row r="6">
@@ -25226,22 +25226,22 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>7814.4</v>
+        <v>13297.8</v>
       </c>
       <c r="M6" t="n">
-        <v>19.2</v>
+        <v>525.6</v>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="O6" t="n">
-        <v>120</v>
+        <v>405</v>
       </c>
       <c r="P6" t="n">
-        <v>2943</v>
+        <v>3487.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4735.71</v>
+        <v>46428.52</v>
       </c>
     </row>
     <row r="7">
@@ -25279,22 +25279,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5022</v>
+        <v>10746</v>
       </c>
       <c r="M7" t="n">
-        <v>21</v>
+        <v>1165.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10.5</v>
+        <v>1018.5</v>
       </c>
       <c r="P7" t="n">
-        <v>5760</v>
+        <v>5820</v>
       </c>
       <c r="Q7" t="n">
-        <v>1987.58</v>
+        <v>19486.08</v>
       </c>
     </row>
     <row r="8">
@@ -25332,22 +25332,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1853.1</v>
+        <v>7455</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27</v>
+        <v>459</v>
       </c>
       <c r="P8" t="n">
-        <v>13338</v>
+        <v>20189.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1057.07</v>
+        <v>10363.46</v>
       </c>
     </row>
     <row r="9">
@@ -25385,10 +25385,10 @@
         <v>0.8</v>
       </c>
       <c r="L9" t="n">
-        <v>874.8</v>
+        <v>2454.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -25397,10 +25397,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4245</v>
+        <v>5055</v>
       </c>
       <c r="Q9" t="n">
-        <v>376.13</v>
+        <v>3687.55</v>
       </c>
     </row>
     <row r="10">
@@ -25438,10 +25438,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>320.4</v>
+        <v>720.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>9460.5</v>
+        <v>11679</v>
       </c>
       <c r="Q10" t="n">
-        <v>189.48</v>
+        <v>1857.6</v>
       </c>
     </row>
     <row r="11">
@@ -25491,7 +25491,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -25503,10 +25503,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5670</v>
+        <v>9747</v>
       </c>
       <c r="Q11" t="n">
-        <v>100.8</v>
+        <v>988.2</v>
       </c>
     </row>
     <row r="12">
@@ -25544,7 +25544,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -25556,10 +25556,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4080</v>
+        <v>6270</v>
       </c>
       <c r="Q12" t="n">
-        <v>58.38</v>
+        <v>572.4</v>
       </c>
     </row>
     <row r="13">
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -25609,10 +25609,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2430</v>
+        <v>5520</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.52</v>
+        <v>338.4</v>
       </c>
     </row>
     <row r="14">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.5</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="15">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1231200</v>
+        <v>2277720</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>112504.25</v>
       </c>
       <c r="L5" t="n">
-        <v>2577582</v>
+        <v>3887352</v>
       </c>
       <c r="M5" t="n">
-        <v>25200</v>
+        <v>128730</v>
       </c>
       <c r="N5" t="n">
-        <v>4539</v>
+        <v>5916</v>
       </c>
       <c r="O5" t="n">
-        <v>40290</v>
+        <v>76500</v>
       </c>
       <c r="P5" t="n">
-        <v>24726</v>
+        <v>26754</v>
       </c>
       <c r="Q5" t="n">
-        <v>426922.33</v>
+        <v>4185513</v>
       </c>
     </row>
     <row r="6">
@@ -26518,22 +26518,22 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1406592</v>
+        <v>2393604</v>
       </c>
       <c r="M6" t="n">
-        <v>6720</v>
+        <v>183960</v>
       </c>
       <c r="N6" t="n">
-        <v>5100</v>
+        <v>9180</v>
       </c>
       <c r="O6" t="n">
-        <v>20400</v>
+        <v>68850</v>
       </c>
       <c r="P6" t="n">
-        <v>191295</v>
+        <v>226687.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2841425.73</v>
+        <v>27857115</v>
       </c>
     </row>
     <row r="7">
@@ -26571,22 +26571,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>903960</v>
+        <v>1934280</v>
       </c>
       <c r="M7" t="n">
-        <v>7350</v>
+        <v>407925</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1785</v>
+        <v>173145</v>
       </c>
       <c r="P7" t="n">
-        <v>374400</v>
+        <v>378300</v>
       </c>
       <c r="Q7" t="n">
-        <v>1192548.1</v>
+        <v>11691648</v>
       </c>
     </row>
     <row r="8">
@@ -26624,22 +26624,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>333558</v>
+        <v>1341900</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>288750</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4590</v>
+        <v>78030</v>
       </c>
       <c r="P8" t="n">
-        <v>866970</v>
+        <v>1312311</v>
       </c>
       <c r="Q8" t="n">
-        <v>634243.45</v>
+        <v>6218073</v>
       </c>
     </row>
     <row r="9">
@@ -26677,10 +26677,10 @@
         <v>38990.47</v>
       </c>
       <c r="L9" t="n">
-        <v>157464</v>
+        <v>441774</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>110250</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -26689,10 +26689,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>275925</v>
+        <v>328575</v>
       </c>
       <c r="Q9" t="n">
-        <v>225678.18</v>
+        <v>2212531.2</v>
       </c>
     </row>
     <row r="10">
@@ -26730,10 +26730,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>57672</v>
+        <v>129762</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>17850</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -26742,10 +26742,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>614932.5</v>
+        <v>759135</v>
       </c>
       <c r="Q10" t="n">
-        <v>113685.12</v>
+        <v>1114560</v>
       </c>
     </row>
     <row r="11">
@@ -26783,7 +26783,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -26795,10 +26795,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>368550</v>
+        <v>633555</v>
       </c>
       <c r="Q11" t="n">
-        <v>60477.84</v>
+        <v>592920</v>
       </c>
     </row>
     <row r="12">
@@ -26836,7 +26836,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -26848,10 +26848,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>265200</v>
+        <v>407550</v>
       </c>
       <c r="Q12" t="n">
-        <v>35030.88</v>
+        <v>343440</v>
       </c>
     </row>
     <row r="13">
@@ -26889,7 +26889,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -26901,10 +26901,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>157950</v>
+        <v>358800</v>
       </c>
       <c r="Q13" t="n">
-        <v>20710.08</v>
+        <v>203040</v>
       </c>
     </row>
     <row r="14">
@@ -26957,7 +26957,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14100.48</v>
+        <v>138240</v>
       </c>
     </row>
     <row r="15">
@@ -27692,7 +27692,7 @@
         <v>86430</v>
       </c>
       <c r="H4" t="n">
-        <v>29100</v>
+        <v>31230</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27704,7 +27704,7 @@
         <v>47</v>
       </c>
       <c r="L4" t="n">
-        <v>240270</v>
+        <v>295350</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>83310</v>
+        <v>93660</v>
       </c>
       <c r="P4" t="n">
-        <v>2190</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>19296.18</v>
+        <v>268681.05</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>28320</v>
       </c>
       <c r="H5" t="n">
-        <v>3390</v>
+        <v>4710</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>63570</v>
+        <v>76710</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>29790</v>
+        <v>37470</v>
       </c>
       <c r="P5" t="n">
-        <v>2820</v>
+        <v>210</v>
       </c>
       <c r="Q5" t="n">
-        <v>5485.86</v>
+        <v>76385.42999999999</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>870</v>
       </c>
       <c r="H6" t="n">
-        <v>540</v>
+        <v>750</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7110</v>
+        <v>11610</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8610</v>
+        <v>15840</v>
       </c>
       <c r="P6" t="n">
-        <v>5040</v>
+        <v>930</v>
       </c>
       <c r="Q6" t="n">
-        <v>283.69</v>
+        <v>3950.1</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>300</v>
       </c>
       <c r="H7" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2850</v>
+        <v>4620</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2310</v>
+        <v>8040</v>
       </c>
       <c r="P7" t="n">
-        <v>5280</v>
+        <v>1740</v>
       </c>
       <c r="Q7" t="n">
-        <v>46.85</v>
+        <v>652.41</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>540</v>
+        <v>2490</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>360</v>
+        <v>2970</v>
       </c>
       <c r="P8" t="n">
-        <v>6210</v>
+        <v>9060</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.84</v>
+        <v>262.35</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>180</v>
+        <v>1440</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P9" t="n">
-        <v>3150</v>
+        <v>8610</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.98</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1740</v>
+        <v>5880</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.64</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="11">
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>390</v>
+        <v>1650</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="12">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1220.4</v>
+        <v>1695.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>13349.7</v>
+        <v>16109.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1489.5</v>
+        <v>1873.5</v>
       </c>
       <c r="P5" t="n">
-        <v>56.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>274.29</v>
+        <v>3819.27</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>43.5</v>
       </c>
       <c r="H6" t="n">
-        <v>307.8</v>
+        <v>427.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2630.7</v>
+        <v>4295.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2152.5</v>
+        <v>3960</v>
       </c>
       <c r="P6" t="n">
-        <v>756</v>
+        <v>139.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>212.77</v>
+        <v>2962.58</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>45</v>
       </c>
       <c r="H7" t="n">
-        <v>219</v>
+        <v>262.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1710</v>
+        <v>2772</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>808.5</v>
+        <v>2814</v>
       </c>
       <c r="P7" t="n">
-        <v>1320</v>
+        <v>435</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.48</v>
+        <v>521.9299999999999</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>19.5</v>
       </c>
       <c r="H8" t="n">
-        <v>25.5</v>
+        <v>127.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>383.4</v>
+        <v>1767.9</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>162</v>
+        <v>1336.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2359.8</v>
+        <v>3442.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.9</v>
+        <v>249.23</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>145.8</v>
+        <v>1166.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="P9" t="n">
-        <v>1575</v>
+        <v>4305</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.83</v>
+        <v>67.22</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26.7</v>
+        <v>1014.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29326,10 +29326,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1479</v>
+        <v>4998</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.64</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="11">
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>351</v>
+        <v>1485</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="12">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6956280</v>
+        <v>9664920</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>2402946</v>
+        <v>2899638</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>253215</v>
+        <v>318495</v>
       </c>
       <c r="P5" t="n">
-        <v>3666</v>
+        <v>273</v>
       </c>
       <c r="Q5" t="n">
-        <v>164575.88</v>
+        <v>2291562.9</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>2349</v>
       </c>
       <c r="H6" t="n">
-        <v>1754460</v>
+        <v>2436750</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>473526</v>
+        <v>773226</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>365925</v>
+        <v>673200</v>
       </c>
       <c r="P6" t="n">
-        <v>49140</v>
+        <v>9067.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>127660.05</v>
+        <v>1777545</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>2430</v>
       </c>
       <c r="H7" t="n">
-        <v>1248300</v>
+        <v>1497960</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>307800</v>
+        <v>498960</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>137445</v>
+        <v>478380</v>
       </c>
       <c r="P7" t="n">
-        <v>85800</v>
+        <v>28275</v>
       </c>
       <c r="Q7" t="n">
-        <v>22490.35</v>
+        <v>313156.8</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>1053</v>
       </c>
       <c r="H8" t="n">
-        <v>145350</v>
+        <v>726750</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>69012</v>
+        <v>318222</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27540</v>
+        <v>227205</v>
       </c>
       <c r="P8" t="n">
-        <v>153387</v>
+        <v>223782</v>
       </c>
       <c r="Q8" t="n">
-        <v>10739.66</v>
+        <v>149539.5</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>171000</v>
+        <v>1368000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26244</v>
+        <v>209952</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>11220</v>
       </c>
       <c r="P9" t="n">
-        <v>102375</v>
+        <v>279825</v>
       </c>
       <c r="Q9" t="n">
-        <v>2896.61</v>
+        <v>40332.6</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4806</v>
+        <v>182628</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30618,10 +30618,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>96135</v>
+        <v>324870</v>
       </c>
       <c r="Q10" t="n">
-        <v>383.94</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="11">
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>48600</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>22815</v>
+        <v>96525</v>
       </c>
       <c r="Q11" t="n">
-        <v>127.98</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="12">
